--- a/public/raw/match2(KarnaliYaksvsChitwanRhinos)/match2(KarnaliYaksvsChitwanRhinos).xlsx
+++ b/public/raw/match2(KarnaliYaksvsChitwanRhinos)/match2(KarnaliYaksvsChitwanRhinos).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shiji\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A346F86-7837-4508-B516-BD2E5F42C005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F571F550-9CB1-4961-8E6D-C7FE214724B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4465" uniqueCount="989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4465" uniqueCount="987">
   <si>
     <t>Date</t>
   </si>
@@ -508,15 +508,9 @@
     <t>Somany Tiles and Bathware</t>
   </si>
   <si>
-    <t>Builiding Material &amp; Sanitaryware</t>
-  </si>
-  <si>
     <t>Tiles and Bathware</t>
   </si>
   <si>
-    <t>Retail and wholesale</t>
-  </si>
-  <si>
     <t>12:15:22</t>
   </si>
   <si>
@@ -1033,9 +1027,6 @@
     <t>12:40:45</t>
   </si>
   <si>
-    <t>ground</t>
-  </si>
-  <si>
     <t>12:41:20</t>
   </si>
   <si>
@@ -2990,6 +2981,9 @@
   </si>
   <si>
     <t>Hospitality</t>
+  </si>
+  <si>
+    <t>Builiding Material</t>
   </si>
 </sst>
 </file>
@@ -3446,7 +3440,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E3">
         <v>12</v>
@@ -3638,7 +3632,7 @@
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E9">
         <v>22</v>
@@ -3894,7 +3888,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -3990,7 +3984,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E20">
         <v>9</v>
@@ -4118,7 +4112,7 @@
         <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E24">
         <v>11</v>
@@ -4150,7 +4144,7 @@
         <v>37</v>
       </c>
       <c r="D25" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E25">
         <v>4</v>
@@ -4182,7 +4176,7 @@
         <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E26">
         <v>6</v>
@@ -4278,7 +4272,7 @@
         <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E29">
         <v>16</v>
@@ -4406,7 +4400,7 @@
         <v>42</v>
       </c>
       <c r="D33" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E33">
         <v>4</v>
@@ -4470,7 +4464,7 @@
         <v>50</v>
       </c>
       <c r="D35" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -4502,7 +4496,7 @@
         <v>52</v>
       </c>
       <c r="D36" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E36">
         <v>4</v>
@@ -4534,7 +4528,7 @@
         <v>53</v>
       </c>
       <c r="D37" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E37">
         <v>9</v>
@@ -5110,7 +5104,7 @@
         <v>70</v>
       </c>
       <c r="D55" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E55">
         <v>16</v>
@@ -5302,7 +5296,7 @@
         <v>73</v>
       </c>
       <c r="D61" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E61">
         <v>7</v>
@@ -5366,7 +5360,7 @@
         <v>75</v>
       </c>
       <c r="D63" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E63">
         <v>9</v>
@@ -5398,7 +5392,7 @@
         <v>77</v>
       </c>
       <c r="D64" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E64">
         <v>9</v>
@@ -5465,7 +5459,7 @@
         <v>86</v>
       </c>
       <c r="D66" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E66">
         <v>6</v>
@@ -5477,7 +5471,7 @@
         <v>81</v>
       </c>
       <c r="H66" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I66" t="s">
         <v>87</v>
@@ -5500,7 +5494,7 @@
         <v>90</v>
       </c>
       <c r="D67" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E67">
         <v>4</v>
@@ -5640,7 +5634,7 @@
         <v>105</v>
       </c>
       <c r="D71" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E71">
         <v>4</v>
@@ -5652,7 +5646,7 @@
         <v>81</v>
       </c>
       <c r="H71" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I71" t="s">
         <v>87</v>
@@ -5722,7 +5716,7 @@
         <v>81</v>
       </c>
       <c r="H73" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I73" t="s">
         <v>87</v>
@@ -5920,7 +5914,7 @@
         <v>130</v>
       </c>
       <c r="D79" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E79">
         <v>2</v>
@@ -5955,7 +5949,7 @@
         <v>132</v>
       </c>
       <c r="D80" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E80">
         <v>5</v>
@@ -5967,7 +5961,7 @@
         <v>81</v>
       </c>
       <c r="H80" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I80" t="s">
         <v>87</v>
@@ -6002,7 +5996,7 @@
         <v>81</v>
       </c>
       <c r="H81" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I81" t="s">
         <v>136</v>
@@ -6247,13 +6241,13 @@
         <v>81</v>
       </c>
       <c r="H88" t="s">
+        <v>986</v>
+      </c>
+      <c r="I88" t="s">
         <v>161</v>
       </c>
-      <c r="I88" t="s">
-        <v>162</v>
-      </c>
       <c r="J88" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="M88">
         <v>1</v>
@@ -6264,13 +6258,13 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C89" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D89" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E89">
         <v>6</v>
@@ -6282,7 +6276,7 @@
         <v>81</v>
       </c>
       <c r="H89" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I89" t="s">
         <v>87</v>
@@ -6299,13 +6293,13 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C90" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D90" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E90">
         <v>2</v>
@@ -6334,13 +6328,13 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
+        <v>166</v>
+      </c>
+      <c r="C91" t="s">
+        <v>167</v>
+      </c>
+      <c r="D91" t="s">
         <v>168</v>
-      </c>
-      <c r="C91" t="s">
-        <v>169</v>
-      </c>
-      <c r="D91" t="s">
-        <v>170</v>
       </c>
       <c r="E91">
         <v>7</v>
@@ -6369,10 +6363,10 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C92" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D92" t="s">
         <v>45</v>
@@ -6404,10 +6398,10 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C93" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D93" t="s">
         <v>80</v>
@@ -6439,10 +6433,10 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C94" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D94" t="s">
         <v>80</v>
@@ -6474,10 +6468,10 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C95" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D95" t="s">
         <v>60</v>
@@ -6509,10 +6503,10 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C96" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D96" t="s">
         <v>108</v>
@@ -6544,10 +6538,10 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C97" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D97" t="s">
         <v>160</v>
@@ -6562,13 +6556,13 @@
         <v>81</v>
       </c>
       <c r="H97" t="s">
+        <v>986</v>
+      </c>
+      <c r="I97" t="s">
         <v>161</v>
       </c>
-      <c r="I97" t="s">
-        <v>162</v>
-      </c>
       <c r="J97" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="M97">
         <v>1</v>
@@ -6579,10 +6573,10 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C98" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D98" t="s">
         <v>35</v>
@@ -6600,7 +6594,7 @@
         <v>152</v>
       </c>
       <c r="I98" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J98" t="s">
         <v>84</v>
@@ -6614,10 +6608,10 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C99" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D99" t="s">
         <v>80</v>
@@ -6649,10 +6643,10 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C100" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D100" t="s">
         <v>60</v>
@@ -6684,13 +6678,13 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
+        <v>188</v>
+      </c>
+      <c r="C101" t="s">
+        <v>189</v>
+      </c>
+      <c r="D101" t="s">
         <v>190</v>
-      </c>
-      <c r="C101" t="s">
-        <v>191</v>
-      </c>
-      <c r="D101" t="s">
-        <v>192</v>
       </c>
       <c r="E101">
         <v>12</v>
@@ -6705,7 +6699,7 @@
         <v>140</v>
       </c>
       <c r="I101" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J101" t="s">
         <v>142</v>
@@ -6719,10 +6713,10 @@
         <v>13</v>
       </c>
       <c r="B102" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C102" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D102" t="s">
         <v>71</v>
@@ -6754,13 +6748,13 @@
         <v>13</v>
       </c>
       <c r="B103" t="s">
+        <v>194</v>
+      </c>
+      <c r="C103" t="s">
+        <v>195</v>
+      </c>
+      <c r="D103" t="s">
         <v>196</v>
-      </c>
-      <c r="C103" t="s">
-        <v>197</v>
-      </c>
-      <c r="D103" t="s">
-        <v>198</v>
       </c>
       <c r="E103">
         <v>5</v>
@@ -6772,10 +6766,10 @@
         <v>81</v>
       </c>
       <c r="H103" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I103" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J103" t="s">
         <v>97</v>
@@ -6789,13 +6783,13 @@
         <v>13</v>
       </c>
       <c r="B104" t="s">
+        <v>199</v>
+      </c>
+      <c r="C104" t="s">
+        <v>200</v>
+      </c>
+      <c r="D104" t="s">
         <v>201</v>
-      </c>
-      <c r="C104" t="s">
-        <v>202</v>
-      </c>
-      <c r="D104" t="s">
-        <v>203</v>
       </c>
       <c r="E104">
         <v>4</v>
@@ -6807,7 +6801,7 @@
         <v>81</v>
       </c>
       <c r="H104" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I104" t="s">
         <v>87</v>
@@ -6824,10 +6818,10 @@
         <v>13</v>
       </c>
       <c r="B105" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C105" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D105" t="s">
         <v>80</v>
@@ -6859,10 +6853,10 @@
         <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C106" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D106" t="s">
         <v>16</v>
@@ -6894,10 +6888,10 @@
         <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C107" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D107" t="s">
         <v>45</v>
@@ -6929,13 +6923,13 @@
         <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C108" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D108" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E108">
         <v>3</v>
@@ -6964,13 +6958,13 @@
         <v>13</v>
       </c>
       <c r="B109" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C109" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D109" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E109">
         <v>6</v>
@@ -6982,7 +6976,7 @@
         <v>81</v>
       </c>
       <c r="H109" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I109" t="s">
         <v>87</v>
@@ -6999,10 +6993,10 @@
         <v>13</v>
       </c>
       <c r="B110" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C110" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D110" t="s">
         <v>63</v>
@@ -7034,10 +7028,10 @@
         <v>13</v>
       </c>
       <c r="B111" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C111" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D111" t="s">
         <v>139</v>
@@ -7069,10 +7063,10 @@
         <v>13</v>
       </c>
       <c r="B112" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C112" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D112" t="s">
         <v>80</v>
@@ -7104,13 +7098,13 @@
         <v>13</v>
       </c>
       <c r="B113" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C113" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D113" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E113">
         <v>6</v>
@@ -7122,7 +7116,7 @@
         <v>81</v>
       </c>
       <c r="H113" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I113" t="s">
         <v>87</v>
@@ -7139,10 +7133,10 @@
         <v>13</v>
       </c>
       <c r="B114" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C114" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D114" t="s">
         <v>63</v>
@@ -7174,10 +7168,10 @@
         <v>13</v>
       </c>
       <c r="B115" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C115" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D115" t="s">
         <v>151</v>
@@ -7209,10 +7203,10 @@
         <v>13</v>
       </c>
       <c r="B116" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C116" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D116" t="s">
         <v>156</v>
@@ -7244,10 +7238,10 @@
         <v>13</v>
       </c>
       <c r="B117" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C117" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D117" t="s">
         <v>16</v>
@@ -7279,10 +7273,10 @@
         <v>13</v>
       </c>
       <c r="B118" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C118" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D118" t="s">
         <v>80</v>
@@ -7314,10 +7308,10 @@
         <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C119" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D119" t="s">
         <v>80</v>
@@ -7349,10 +7343,10 @@
         <v>13</v>
       </c>
       <c r="B120" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C120" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D120" t="s">
         <v>60</v>
@@ -7384,10 +7378,10 @@
         <v>13</v>
       </c>
       <c r="B121" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C121" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D121" t="s">
         <v>108</v>
@@ -7419,10 +7413,10 @@
         <v>13</v>
       </c>
       <c r="B122" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C122" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D122" t="s">
         <v>160</v>
@@ -7437,13 +7431,13 @@
         <v>81</v>
       </c>
       <c r="H122" t="s">
+        <v>986</v>
+      </c>
+      <c r="I122" t="s">
         <v>161</v>
       </c>
-      <c r="I122" t="s">
-        <v>162</v>
-      </c>
       <c r="J122" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="M122">
         <v>1</v>
@@ -7454,10 +7448,10 @@
         <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C123" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D123" t="s">
         <v>35</v>
@@ -7475,7 +7469,7 @@
         <v>152</v>
       </c>
       <c r="I123" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J123" t="s">
         <v>84</v>
@@ -7489,10 +7483,10 @@
         <v>13</v>
       </c>
       <c r="B124" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C124" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D124" t="s">
         <v>16</v>
@@ -7524,10 +7518,10 @@
         <v>13</v>
       </c>
       <c r="B125" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C125" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D125" t="s">
         <v>80</v>
@@ -7559,10 +7553,10 @@
         <v>13</v>
       </c>
       <c r="B126" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C126" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D126" t="s">
         <v>45</v>
@@ -7594,10 +7588,10 @@
         <v>13</v>
       </c>
       <c r="B127" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C127" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D127" t="s">
         <v>71</v>
@@ -7629,13 +7623,13 @@
         <v>13</v>
       </c>
       <c r="B128" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C128" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D128" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E128">
         <v>4</v>
@@ -7647,7 +7641,7 @@
         <v>81</v>
       </c>
       <c r="H128" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I128" t="s">
         <v>87</v>
@@ -7664,10 +7658,10 @@
         <v>13</v>
       </c>
       <c r="B129" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C129" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D129" t="s">
         <v>80</v>
@@ -7699,10 +7693,10 @@
         <v>13</v>
       </c>
       <c r="B130" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C130" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D130" t="s">
         <v>60</v>
@@ -7734,13 +7728,13 @@
         <v>13</v>
       </c>
       <c r="B131" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C131" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D131" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E131">
         <v>3</v>
@@ -7769,13 +7763,13 @@
         <v>13</v>
       </c>
       <c r="B132" t="s">
+        <v>256</v>
+      </c>
+      <c r="C132" t="s">
+        <v>257</v>
+      </c>
+      <c r="D132" t="s">
         <v>258</v>
-      </c>
-      <c r="C132" t="s">
-        <v>259</v>
-      </c>
-      <c r="D132" t="s">
-        <v>260</v>
       </c>
       <c r="E132">
         <v>11</v>
@@ -7790,7 +7784,7 @@
         <v>109</v>
       </c>
       <c r="I132" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J132" t="s">
         <v>111</v>
@@ -7804,10 +7798,10 @@
         <v>13</v>
       </c>
       <c r="B133" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C133" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D133" t="s">
         <v>80</v>
@@ -7839,10 +7833,10 @@
         <v>13</v>
       </c>
       <c r="B134" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C134" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D134" t="s">
         <v>45</v>
@@ -7860,7 +7854,7 @@
         <v>18</v>
       </c>
       <c r="L134" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M134">
         <v>1</v>
@@ -7871,13 +7865,13 @@
         <v>13</v>
       </c>
       <c r="B135" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C135" t="s">
+        <v>262</v>
+      </c>
+      <c r="D135" t="s">
         <v>264</v>
-      </c>
-      <c r="D135" t="s">
-        <v>266</v>
       </c>
       <c r="E135">
         <v>3</v>
@@ -7892,7 +7886,7 @@
         <v>18</v>
       </c>
       <c r="L135" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M135">
         <v>1</v>
@@ -7903,10 +7897,10 @@
         <v>13</v>
       </c>
       <c r="B136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C136" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D136" t="s">
         <v>22</v>
@@ -7924,7 +7918,7 @@
         <v>18</v>
       </c>
       <c r="L136" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M136">
         <v>1</v>
@@ -7935,10 +7929,10 @@
         <v>13</v>
       </c>
       <c r="B137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D137" t="s">
         <v>35</v>
@@ -7956,7 +7950,7 @@
         <v>18</v>
       </c>
       <c r="L137" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M137">
         <v>1</v>
@@ -7967,10 +7961,10 @@
         <v>13</v>
       </c>
       <c r="B138" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C138" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D138" t="s">
         <v>80</v>
@@ -7988,7 +7982,7 @@
         <v>18</v>
       </c>
       <c r="L138" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M138">
         <v>1</v>
@@ -7999,13 +7993,13 @@
         <v>13</v>
       </c>
       <c r="B139" t="s">
+        <v>268</v>
+      </c>
+      <c r="C139" t="s">
+        <v>269</v>
+      </c>
+      <c r="D139" t="s">
         <v>270</v>
-      </c>
-      <c r="C139" t="s">
-        <v>271</v>
-      </c>
-      <c r="D139" t="s">
-        <v>272</v>
       </c>
       <c r="E139">
         <v>3</v>
@@ -8020,7 +8014,7 @@
         <v>18</v>
       </c>
       <c r="L139" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M139">
         <v>1</v>
@@ -8031,13 +8025,13 @@
         <v>13</v>
       </c>
       <c r="B140" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C140" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D140" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E140">
         <v>7</v>
@@ -8049,7 +8043,7 @@
         <v>81</v>
       </c>
       <c r="H140" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I140" t="s">
         <v>87</v>
@@ -8066,10 +8060,10 @@
         <v>13</v>
       </c>
       <c r="B141" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C141" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D141" t="s">
         <v>63</v>
@@ -8101,10 +8095,10 @@
         <v>13</v>
       </c>
       <c r="B142" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C142" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D142" t="s">
         <v>151</v>
@@ -8136,10 +8130,10 @@
         <v>13</v>
       </c>
       <c r="B143" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C143" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D143" t="s">
         <v>156</v>
@@ -8171,13 +8165,13 @@
         <v>13</v>
       </c>
       <c r="B144" t="s">
+        <v>280</v>
+      </c>
+      <c r="C144" t="s">
+        <v>281</v>
+      </c>
+      <c r="D144" t="s">
         <v>282</v>
-      </c>
-      <c r="C144" t="s">
-        <v>283</v>
-      </c>
-      <c r="D144" t="s">
-        <v>284</v>
       </c>
       <c r="E144">
         <v>10</v>
@@ -8192,7 +8186,7 @@
         <v>18</v>
       </c>
       <c r="L144" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M144">
         <v>1</v>
@@ -8203,13 +8197,13 @@
         <v>13</v>
       </c>
       <c r="B145" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C145" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D145" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E145">
         <v>4</v>
@@ -8224,7 +8218,7 @@
         <v>18</v>
       </c>
       <c r="L145" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M145">
         <v>1</v>
@@ -8235,10 +8229,10 @@
         <v>13</v>
       </c>
       <c r="B146" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C146" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D146" t="s">
         <v>45</v>
@@ -8256,7 +8250,7 @@
         <v>18</v>
       </c>
       <c r="L146" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M146">
         <v>1</v>
@@ -8267,13 +8261,13 @@
         <v>13</v>
       </c>
       <c r="B147" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C147" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D147" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E147">
         <v>6</v>
@@ -8288,7 +8282,7 @@
         <v>18</v>
       </c>
       <c r="L147" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M147">
         <v>1</v>
@@ -8299,10 +8293,10 @@
         <v>13</v>
       </c>
       <c r="B148" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C148" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D148" t="s">
         <v>108</v>
@@ -8320,7 +8314,7 @@
         <v>18</v>
       </c>
       <c r="L148" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M148">
         <v>1</v>
@@ -8331,13 +8325,13 @@
         <v>13</v>
       </c>
       <c r="B149" t="s">
+        <v>292</v>
+      </c>
+      <c r="C149" t="s">
+        <v>293</v>
+      </c>
+      <c r="D149" t="s">
         <v>294</v>
-      </c>
-      <c r="C149" t="s">
-        <v>295</v>
-      </c>
-      <c r="D149" t="s">
-        <v>296</v>
       </c>
       <c r="E149">
         <v>5</v>
@@ -8352,7 +8346,7 @@
         <v>18</v>
       </c>
       <c r="L149" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M149">
         <v>1</v>
@@ -8363,10 +8357,10 @@
         <v>13</v>
       </c>
       <c r="B150" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C150" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D150" t="s">
         <v>80</v>
@@ -8384,7 +8378,7 @@
         <v>18</v>
       </c>
       <c r="L150" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M150">
         <v>1</v>
@@ -8395,10 +8389,10 @@
         <v>13</v>
       </c>
       <c r="B151" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C151" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D151" t="s">
         <v>92</v>
@@ -8416,7 +8410,7 @@
         <v>18</v>
       </c>
       <c r="L151" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M151">
         <v>1</v>
@@ -8427,10 +8421,10 @@
         <v>13</v>
       </c>
       <c r="B152" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C152" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D152" t="s">
         <v>16</v>
@@ -8448,7 +8442,7 @@
         <v>18</v>
       </c>
       <c r="L152" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M152">
         <v>1</v>
@@ -8459,13 +8453,13 @@
         <v>13</v>
       </c>
       <c r="B153" t="s">
+        <v>301</v>
+      </c>
+      <c r="C153" t="s">
+        <v>302</v>
+      </c>
+      <c r="D153" t="s">
         <v>303</v>
-      </c>
-      <c r="C153" t="s">
-        <v>304</v>
-      </c>
-      <c r="D153" t="s">
-        <v>305</v>
       </c>
       <c r="E153">
         <v>16</v>
@@ -8480,7 +8474,7 @@
         <v>18</v>
       </c>
       <c r="L153" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M153">
         <v>1</v>
@@ -8491,10 +8485,10 @@
         <v>13</v>
       </c>
       <c r="B154" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C154" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D154" t="s">
         <v>45</v>
@@ -8512,7 +8506,7 @@
         <v>18</v>
       </c>
       <c r="L154" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M154">
         <v>1</v>
@@ -8523,10 +8517,10 @@
         <v>13</v>
       </c>
       <c r="B155" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C155" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D155" t="s">
         <v>22</v>
@@ -8555,10 +8549,10 @@
         <v>13</v>
       </c>
       <c r="B156" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C156" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D156" t="s">
         <v>71</v>
@@ -8576,7 +8570,7 @@
         <v>18</v>
       </c>
       <c r="L156" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M156">
         <v>1</v>
@@ -8587,10 +8581,10 @@
         <v>13</v>
       </c>
       <c r="B157" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C157" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D157" t="s">
         <v>80</v>
@@ -8608,7 +8602,7 @@
         <v>18</v>
       </c>
       <c r="L157" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M157">
         <v>1</v>
@@ -8619,10 +8613,10 @@
         <v>13</v>
       </c>
       <c r="B158" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C158" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D158" t="s">
         <v>71</v>
@@ -8640,7 +8634,7 @@
         <v>18</v>
       </c>
       <c r="L158" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M158">
         <v>1</v>
@@ -8651,13 +8645,13 @@
         <v>13</v>
       </c>
       <c r="B159" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C159" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D159" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E159">
         <v>7</v>
@@ -8672,7 +8666,7 @@
         <v>18</v>
       </c>
       <c r="L159" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M159">
         <v>1</v>
@@ -8683,10 +8677,10 @@
         <v>13</v>
       </c>
       <c r="B160" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C160" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D160" t="s">
         <v>22</v>
@@ -8715,10 +8709,10 @@
         <v>13</v>
       </c>
       <c r="B161" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C161" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D161" t="s">
         <v>16</v>
@@ -8736,7 +8730,7 @@
         <v>18</v>
       </c>
       <c r="L161" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M161">
         <v>1</v>
@@ -8747,10 +8741,10 @@
         <v>13</v>
       </c>
       <c r="B162" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C162" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D162" t="s">
         <v>22</v>
@@ -8779,10 +8773,10 @@
         <v>13</v>
       </c>
       <c r="B163" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C163" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D163" t="s">
         <v>16</v>
@@ -8800,7 +8794,7 @@
         <v>18</v>
       </c>
       <c r="L163" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M163">
         <v>1</v>
@@ -8811,13 +8805,13 @@
         <v>13</v>
       </c>
       <c r="B164" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C164" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D164" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E164">
         <v>3</v>
@@ -8832,7 +8826,7 @@
         <v>18</v>
       </c>
       <c r="L164" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M164">
         <v>1</v>
@@ -8843,10 +8837,10 @@
         <v>13</v>
       </c>
       <c r="B165" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C165" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D165" t="s">
         <v>71</v>
@@ -8864,7 +8858,7 @@
         <v>18</v>
       </c>
       <c r="L165" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M165">
         <v>1</v>
@@ -8875,10 +8869,10 @@
         <v>13</v>
       </c>
       <c r="B166" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C166" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D166" t="s">
         <v>22</v>
@@ -8907,10 +8901,10 @@
         <v>13</v>
       </c>
       <c r="B167" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C167" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D167" t="s">
         <v>16</v>
@@ -8928,7 +8922,7 @@
         <v>18</v>
       </c>
       <c r="L167" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M167">
         <v>1</v>
@@ -8939,13 +8933,13 @@
         <v>13</v>
       </c>
       <c r="B168" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C168" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D168" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E168">
         <v>3</v>
@@ -8960,7 +8954,7 @@
         <v>18</v>
       </c>
       <c r="L168" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M168">
         <v>1</v>
@@ -8971,10 +8965,10 @@
         <v>13</v>
       </c>
       <c r="B169" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C169" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D169" t="s">
         <v>71</v>
@@ -8992,7 +8986,7 @@
         <v>18</v>
       </c>
       <c r="L169" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M169">
         <v>1</v>
@@ -9003,13 +8997,13 @@
         <v>13</v>
       </c>
       <c r="B170" t="s">
+        <v>316</v>
+      </c>
+      <c r="C170" t="s">
+        <v>317</v>
+      </c>
+      <c r="D170" t="s">
         <v>318</v>
-      </c>
-      <c r="C170" t="s">
-        <v>319</v>
-      </c>
-      <c r="D170" t="s">
-        <v>320</v>
       </c>
       <c r="E170">
         <v>6</v>
@@ -9024,7 +9018,7 @@
         <v>18</v>
       </c>
       <c r="L170" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M170">
         <v>1</v>
@@ -9035,10 +9029,10 @@
         <v>13</v>
       </c>
       <c r="B171" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C171" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D171" t="s">
         <v>80</v>
@@ -9070,13 +9064,13 @@
         <v>13</v>
       </c>
       <c r="B172" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C172" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D172" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E172">
         <v>5</v>
@@ -9088,7 +9082,7 @@
         <v>81</v>
       </c>
       <c r="H172" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I172" t="s">
         <v>87</v>
@@ -9105,13 +9099,13 @@
         <v>13</v>
       </c>
       <c r="B173" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C173" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D173" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E173">
         <v>3</v>
@@ -9140,10 +9134,10 @@
         <v>13</v>
       </c>
       <c r="B174" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C174" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D174" t="s">
         <v>60</v>
@@ -9175,10 +9169,10 @@
         <v>13</v>
       </c>
       <c r="B175" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C175" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D175" t="s">
         <v>16</v>
@@ -9210,10 +9204,10 @@
         <v>13</v>
       </c>
       <c r="B176" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C176" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D176" t="s">
         <v>71</v>
@@ -9245,10 +9239,10 @@
         <v>13</v>
       </c>
       <c r="B177" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C177" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D177" t="s">
         <v>45</v>
@@ -9266,7 +9260,7 @@
         <v>18</v>
       </c>
       <c r="L177" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M177">
         <v>1</v>
@@ -9277,10 +9271,10 @@
         <v>13</v>
       </c>
       <c r="B178" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C178" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D178" t="s">
         <v>16</v>
@@ -9298,7 +9292,7 @@
         <v>18</v>
       </c>
       <c r="L178" t="s">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="M178">
         <v>1</v>
@@ -9309,10 +9303,10 @@
         <v>13</v>
       </c>
       <c r="B179" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C179" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D179" t="s">
         <v>45</v>
@@ -9330,7 +9324,7 @@
         <v>18</v>
       </c>
       <c r="L179" t="s">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="M179">
         <v>1</v>
@@ -9341,10 +9335,10 @@
         <v>13</v>
       </c>
       <c r="B180" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C180" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D180" t="s">
         <v>45</v>
@@ -9362,7 +9356,7 @@
         <v>18</v>
       </c>
       <c r="L180" t="s">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="M180">
         <v>1</v>
@@ -9373,10 +9367,10 @@
         <v>13</v>
       </c>
       <c r="B181" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C181" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D181" t="s">
         <v>16</v>
@@ -9394,7 +9388,7 @@
         <v>18</v>
       </c>
       <c r="L181" t="s">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="M181">
         <v>1</v>
@@ -9405,10 +9399,10 @@
         <v>13</v>
       </c>
       <c r="B182" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C182" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D182" t="s">
         <v>16</v>
@@ -9426,7 +9420,7 @@
         <v>18</v>
       </c>
       <c r="L182" t="s">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="M182">
         <v>1</v>
@@ -9437,10 +9431,10 @@
         <v>13</v>
       </c>
       <c r="B183" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C183" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D183" t="s">
         <v>45</v>
@@ -9458,7 +9452,7 @@
         <v>18</v>
       </c>
       <c r="L183" t="s">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="M183">
         <v>1</v>
@@ -9469,10 +9463,10 @@
         <v>13</v>
       </c>
       <c r="B184" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C184" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D184" t="s">
         <v>45</v>
@@ -9490,7 +9484,7 @@
         <v>18</v>
       </c>
       <c r="L184" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M184">
         <v>1</v>
@@ -9501,13 +9495,13 @@
         <v>13</v>
       </c>
       <c r="B185" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C185" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D185" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E185">
         <v>4</v>
@@ -9519,7 +9513,7 @@
         <v>81</v>
       </c>
       <c r="H185" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I185" t="s">
         <v>87</v>
@@ -9536,10 +9530,10 @@
         <v>13</v>
       </c>
       <c r="B186" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C186" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D186" t="s">
         <v>108</v>
@@ -9571,10 +9565,10 @@
         <v>13</v>
       </c>
       <c r="B187" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C187" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D187" t="s">
         <v>114</v>
@@ -9589,7 +9583,7 @@
         <v>81</v>
       </c>
       <c r="H187" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I187" t="s">
         <v>87</v>
@@ -9606,10 +9600,10 @@
         <v>13</v>
       </c>
       <c r="B188" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C188" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D188" t="s">
         <v>80</v>
@@ -9641,10 +9635,10 @@
         <v>13</v>
       </c>
       <c r="B189" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C189" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D189" t="s">
         <v>80</v>
@@ -9676,10 +9670,10 @@
         <v>13</v>
       </c>
       <c r="B190" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C190" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D190" t="s">
         <v>60</v>
@@ -9711,10 +9705,10 @@
         <v>13</v>
       </c>
       <c r="B191" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C191" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D191" t="s">
         <v>63</v>
@@ -9746,10 +9740,10 @@
         <v>13</v>
       </c>
       <c r="B192" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C192" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D192" t="s">
         <v>45</v>
@@ -9781,13 +9775,13 @@
         <v>13</v>
       </c>
       <c r="B193" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C193" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D193" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E193">
         <v>2</v>
@@ -9816,13 +9810,13 @@
         <v>13</v>
       </c>
       <c r="B194" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C194" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D194" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E194">
         <v>5</v>
@@ -9834,7 +9828,7 @@
         <v>81</v>
       </c>
       <c r="H194" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I194" t="s">
         <v>87</v>
@@ -9851,13 +9845,13 @@
         <v>13</v>
       </c>
       <c r="B195" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C195" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D195" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E195">
         <v>4</v>
@@ -9869,10 +9863,10 @@
         <v>81</v>
       </c>
       <c r="H195" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I195" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="J195" t="s">
         <v>97</v>
@@ -9886,10 +9880,10 @@
         <v>13</v>
       </c>
       <c r="B196" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C196" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D196" t="s">
         <v>35</v>
@@ -9907,7 +9901,7 @@
         <v>152</v>
       </c>
       <c r="I196" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J196" t="s">
         <v>84</v>
@@ -9921,10 +9915,10 @@
         <v>13</v>
       </c>
       <c r="B197" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C197" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D197" t="s">
         <v>80</v>
@@ -9956,10 +9950,10 @@
         <v>13</v>
       </c>
       <c r="B198" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C198" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D198" t="s">
         <v>80</v>
@@ -9991,10 +9985,10 @@
         <v>13</v>
       </c>
       <c r="B199" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C199" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D199" t="s">
         <v>60</v>
@@ -10026,10 +10020,10 @@
         <v>13</v>
       </c>
       <c r="B200" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C200" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D200" t="s">
         <v>63</v>
@@ -10061,10 +10055,10 @@
         <v>13</v>
       </c>
       <c r="B201" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C201" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D201" t="s">
         <v>151</v>
@@ -10096,10 +10090,10 @@
         <v>13</v>
       </c>
       <c r="B202" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C202" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D202" t="s">
         <v>156</v>
@@ -10131,13 +10125,13 @@
         <v>13</v>
       </c>
       <c r="B203" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C203" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D203" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E203">
         <v>9</v>
@@ -10149,10 +10143,10 @@
         <v>81</v>
       </c>
       <c r="H203" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I203" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="J203" t="s">
         <v>88</v>
@@ -10166,13 +10160,13 @@
         <v>13</v>
       </c>
       <c r="B204" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C204" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D204" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E204">
         <v>5</v>
@@ -10184,10 +10178,10 @@
         <v>81</v>
       </c>
       <c r="H204" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I204" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J204" t="s">
         <v>97</v>
@@ -10201,13 +10195,13 @@
         <v>13</v>
       </c>
       <c r="B205" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C205" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D205" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E205">
         <v>4</v>
@@ -10219,7 +10213,7 @@
         <v>81</v>
       </c>
       <c r="H205" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I205" t="s">
         <v>87</v>
@@ -10236,10 +10230,10 @@
         <v>13</v>
       </c>
       <c r="B206" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C206" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D206" t="s">
         <v>80</v>
@@ -10271,13 +10265,13 @@
         <v>13</v>
       </c>
       <c r="B207" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C207" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D207" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E207">
         <v>21</v>
@@ -10289,10 +10283,10 @@
         <v>81</v>
       </c>
       <c r="H207" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I207" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J207" t="s">
         <v>97</v>
@@ -10306,10 +10300,10 @@
         <v>13</v>
       </c>
       <c r="B208" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C208" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D208" t="s">
         <v>16</v>
@@ -10341,13 +10335,13 @@
         <v>13</v>
       </c>
       <c r="B209" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C209" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D209" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E209">
         <v>2</v>
@@ -10376,13 +10370,13 @@
         <v>13</v>
       </c>
       <c r="B210" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C210" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D210" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E210">
         <v>6</v>
@@ -10394,7 +10388,7 @@
         <v>81</v>
       </c>
       <c r="H210" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I210" t="s">
         <v>87</v>
@@ -10411,13 +10405,13 @@
         <v>13</v>
       </c>
       <c r="B211" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C211" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D211" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E211">
         <v>2</v>
@@ -10429,10 +10423,10 @@
         <v>81</v>
       </c>
       <c r="H211" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I211" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="J211" t="s">
         <v>88</v>
@@ -10446,13 +10440,13 @@
         <v>13</v>
       </c>
       <c r="B212" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C212" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D212" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E212">
         <v>8</v>
@@ -10467,7 +10461,7 @@
         <v>109</v>
       </c>
       <c r="I212" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J212" t="s">
         <v>111</v>
@@ -10481,10 +10475,10 @@
         <v>13</v>
       </c>
       <c r="B213" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C213" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D213" t="s">
         <v>60</v>
@@ -10516,10 +10510,10 @@
         <v>13</v>
       </c>
       <c r="B214" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C214" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D214" t="s">
         <v>80</v>
@@ -10551,10 +10545,10 @@
         <v>13</v>
       </c>
       <c r="B215" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C215" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D215" t="s">
         <v>80</v>
@@ -10586,10 +10580,10 @@
         <v>13</v>
       </c>
       <c r="B216" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C216" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D216" t="s">
         <v>60</v>
@@ -10621,13 +10615,13 @@
         <v>13</v>
       </c>
       <c r="B217" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C217" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D217" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E217">
         <v>9</v>
@@ -10639,10 +10633,10 @@
         <v>81</v>
       </c>
       <c r="H217" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I217" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="J217" t="s">
         <v>84</v>
@@ -10656,13 +10650,13 @@
         <v>13</v>
       </c>
       <c r="B218" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C218" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D218" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E218">
         <v>13</v>
@@ -10677,7 +10671,7 @@
         <v>82</v>
       </c>
       <c r="I218" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J218" t="s">
         <v>84</v>
@@ -10691,13 +10685,13 @@
         <v>13</v>
       </c>
       <c r="B219" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C219" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D219" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E219">
         <v>3</v>
@@ -10709,7 +10703,7 @@
         <v>81</v>
       </c>
       <c r="H219" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I219" t="s">
         <v>87</v>
@@ -10726,10 +10720,10 @@
         <v>13</v>
       </c>
       <c r="B220" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C220" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D220" t="s">
         <v>108</v>
@@ -10761,13 +10755,13 @@
         <v>13</v>
       </c>
       <c r="B221" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C221" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D221" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E221">
         <v>6</v>
@@ -10796,10 +10790,10 @@
         <v>13</v>
       </c>
       <c r="B222" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C222" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D222" t="s">
         <v>63</v>
@@ -10831,10 +10825,10 @@
         <v>13</v>
       </c>
       <c r="B223" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C223" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D223" t="s">
         <v>35</v>
@@ -10852,7 +10846,7 @@
         <v>152</v>
       </c>
       <c r="I223" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J223" t="s">
         <v>84</v>
@@ -10866,10 +10860,10 @@
         <v>13</v>
       </c>
       <c r="B224" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C224" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D224" t="s">
         <v>80</v>
@@ -10901,13 +10895,13 @@
         <v>13</v>
       </c>
       <c r="B225" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C225" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D225" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E225">
         <v>5</v>
@@ -10919,10 +10913,10 @@
         <v>81</v>
       </c>
       <c r="H225" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I225" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J225" t="s">
         <v>97</v>
@@ -10936,13 +10930,13 @@
         <v>13</v>
       </c>
       <c r="B226" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C226" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D226" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E226">
         <v>4</v>
@@ -10954,7 +10948,7 @@
         <v>81</v>
       </c>
       <c r="H226" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I226" t="s">
         <v>87</v>
@@ -10971,10 +10965,10 @@
         <v>13</v>
       </c>
       <c r="B227" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C227" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D227" t="s">
         <v>80</v>
@@ -11006,13 +11000,13 @@
         <v>13</v>
       </c>
       <c r="B228" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C228" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D228" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E228">
         <v>4</v>
@@ -11041,10 +11035,10 @@
         <v>13</v>
       </c>
       <c r="B229" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C229" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D229" t="s">
         <v>156</v>
@@ -11076,13 +11070,13 @@
         <v>13</v>
       </c>
       <c r="B230" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C230" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D230" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E230">
         <v>6</v>
@@ -11094,10 +11088,10 @@
         <v>81</v>
       </c>
       <c r="H230" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I230" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="J230" t="s">
         <v>142</v>
@@ -11111,13 +11105,13 @@
         <v>13</v>
       </c>
       <c r="B231" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C231" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D231" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E231">
         <v>8</v>
@@ -11129,10 +11123,10 @@
         <v>81</v>
       </c>
       <c r="H231" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I231" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="J231" t="s">
         <v>84</v>
@@ -11146,10 +11140,10 @@
         <v>13</v>
       </c>
       <c r="B232" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C232" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D232" t="s">
         <v>80</v>
@@ -11181,10 +11175,10 @@
         <v>13</v>
       </c>
       <c r="B233" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C233" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D233" t="s">
         <v>60</v>
@@ -11216,10 +11210,10 @@
         <v>13</v>
       </c>
       <c r="B234" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C234" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D234" t="s">
         <v>160</v>
@@ -11234,13 +11228,13 @@
         <v>81</v>
       </c>
       <c r="H234" t="s">
+        <v>986</v>
+      </c>
+      <c r="I234" t="s">
         <v>161</v>
       </c>
-      <c r="I234" t="s">
-        <v>162</v>
-      </c>
       <c r="J234" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="M234">
         <v>1</v>
@@ -11251,10 +11245,10 @@
         <v>13</v>
       </c>
       <c r="B235" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C235" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D235" t="s">
         <v>71</v>
@@ -11286,13 +11280,13 @@
         <v>13</v>
       </c>
       <c r="B236" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C236" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D236" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E236">
         <v>6</v>
@@ -11304,10 +11298,10 @@
         <v>81</v>
       </c>
       <c r="H236" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I236" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="J236" t="s">
         <v>142</v>
@@ -11321,13 +11315,13 @@
         <v>13</v>
       </c>
       <c r="B237" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C237" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D237" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E237">
         <v>6</v>
@@ -11347,13 +11341,13 @@
         <v>13</v>
       </c>
       <c r="B238" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C238" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D238" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E238">
         <v>5</v>
@@ -11365,7 +11359,7 @@
         <v>81</v>
       </c>
       <c r="H238" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I238" t="s">
         <v>87</v>
@@ -11382,10 +11376,10 @@
         <v>13</v>
       </c>
       <c r="B239" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C239" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D239" t="s">
         <v>16</v>
@@ -11417,10 +11411,10 @@
         <v>13</v>
       </c>
       <c r="B240" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C240" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D240" t="s">
         <v>60</v>
@@ -11438,7 +11432,7 @@
         <v>95</v>
       </c>
       <c r="I240" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="J240" t="s">
         <v>97</v>
@@ -11452,13 +11446,13 @@
         <v>13</v>
       </c>
       <c r="B241" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C241" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D241" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E241">
         <v>10</v>
@@ -11470,7 +11464,7 @@
         <v>81</v>
       </c>
       <c r="H241" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I241" t="s">
         <v>136</v>
@@ -11487,10 +11481,10 @@
         <v>13</v>
       </c>
       <c r="B242" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C242" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D242" t="s">
         <v>80</v>
@@ -11522,10 +11516,10 @@
         <v>13</v>
       </c>
       <c r="B243" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C243" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D243" t="s">
         <v>16</v>
@@ -11543,7 +11537,7 @@
         <v>100</v>
       </c>
       <c r="I243" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="J243" t="s">
         <v>88</v>
@@ -11557,10 +11551,10 @@
         <v>13</v>
       </c>
       <c r="B244" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C244" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D244" t="s">
         <v>45</v>
@@ -11592,10 +11586,10 @@
         <v>13</v>
       </c>
       <c r="B245" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C245" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D245" t="s">
         <v>71</v>
@@ -11627,13 +11621,13 @@
         <v>13</v>
       </c>
       <c r="B246" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C246" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D246" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E246">
         <v>6</v>
@@ -11645,7 +11639,7 @@
         <v>81</v>
       </c>
       <c r="H246" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I246" t="s">
         <v>87</v>
@@ -11662,13 +11656,13 @@
         <v>13</v>
       </c>
       <c r="B247" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C247" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D247" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E247">
         <v>6</v>
@@ -11697,10 +11691,10 @@
         <v>13</v>
       </c>
       <c r="B248" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C248" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D248" t="s">
         <v>60</v>
@@ -11718,7 +11712,7 @@
         <v>95</v>
       </c>
       <c r="I248" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="J248" t="s">
         <v>97</v>
@@ -11732,10 +11726,10 @@
         <v>13</v>
       </c>
       <c r="B249" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C249" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D249" t="s">
         <v>80</v>
@@ -11767,13 +11761,13 @@
         <v>13</v>
       </c>
       <c r="B250" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C250" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D250" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E250">
         <v>8</v>
@@ -11788,7 +11782,7 @@
         <v>109</v>
       </c>
       <c r="I250" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J250" t="s">
         <v>111</v>
@@ -11802,13 +11796,13 @@
         <v>13</v>
       </c>
       <c r="B251" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C251" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D251" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E251">
         <v>5</v>
@@ -11820,7 +11814,7 @@
         <v>81</v>
       </c>
       <c r="H251" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I251" t="s">
         <v>87</v>
@@ -11837,13 +11831,13 @@
         <v>13</v>
       </c>
       <c r="B252" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C252" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D252" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E252">
         <v>30</v>
@@ -11855,10 +11849,10 @@
         <v>81</v>
       </c>
       <c r="H252" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I252" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J252" t="s">
         <v>97</v>
@@ -11872,10 +11866,10 @@
         <v>13</v>
       </c>
       <c r="B253" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C253" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D253" t="s">
         <v>80</v>
@@ -11907,13 +11901,13 @@
         <v>13</v>
       </c>
       <c r="B254" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C254" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D254" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E254">
         <v>4</v>
@@ -11925,7 +11919,7 @@
         <v>81</v>
       </c>
       <c r="H254" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I254" t="s">
         <v>87</v>
@@ -11942,10 +11936,10 @@
         <v>13</v>
       </c>
       <c r="B255" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C255" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D255" t="s">
         <v>108</v>
@@ -11977,10 +11971,10 @@
         <v>13</v>
       </c>
       <c r="B256" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C256" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D256" t="s">
         <v>63</v>
@@ -12012,13 +12006,13 @@
         <v>13</v>
       </c>
       <c r="B257" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C257" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D257" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E257">
         <v>7</v>
@@ -12030,10 +12024,10 @@
         <v>81</v>
       </c>
       <c r="H257" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I257" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="J257" t="s">
         <v>84</v>
@@ -12047,10 +12041,10 @@
         <v>13</v>
       </c>
       <c r="B258" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C258" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D258" t="s">
         <v>151</v>
@@ -12082,13 +12076,13 @@
         <v>13</v>
       </c>
       <c r="B259" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C259" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D259" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E259">
         <v>5</v>
@@ -12100,7 +12094,7 @@
         <v>81</v>
       </c>
       <c r="H259" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I259" t="s">
         <v>87</v>
@@ -12117,13 +12111,13 @@
         <v>13</v>
       </c>
       <c r="B260" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C260" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D260" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E260">
         <v>4</v>
@@ -12152,10 +12146,10 @@
         <v>13</v>
       </c>
       <c r="B261" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C261" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D261" t="s">
         <v>80</v>
@@ -12187,10 +12181,10 @@
         <v>13</v>
       </c>
       <c r="B262" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C262" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D262" t="s">
         <v>16</v>
@@ -12222,10 +12216,10 @@
         <v>13</v>
       </c>
       <c r="B263" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C263" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D263" t="s">
         <v>45</v>
@@ -12257,10 +12251,10 @@
         <v>13</v>
       </c>
       <c r="B264" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C264" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D264" t="s">
         <v>71</v>
@@ -12292,28 +12286,28 @@
         <v>13</v>
       </c>
       <c r="B265" t="s">
+        <v>521</v>
+      </c>
+      <c r="C265" t="s">
+        <v>522</v>
+      </c>
+      <c r="D265" t="s">
+        <v>523</v>
+      </c>
+      <c r="E265">
+        <v>13</v>
+      </c>
+      <c r="F265" t="s">
+        <v>17</v>
+      </c>
+      <c r="G265" t="s">
+        <v>81</v>
+      </c>
+      <c r="H265" t="s">
         <v>524</v>
       </c>
-      <c r="C265" t="s">
+      <c r="I265" t="s">
         <v>525</v>
-      </c>
-      <c r="D265" t="s">
-        <v>526</v>
-      </c>
-      <c r="E265">
-        <v>13</v>
-      </c>
-      <c r="F265" t="s">
-        <v>17</v>
-      </c>
-      <c r="G265" t="s">
-        <v>81</v>
-      </c>
-      <c r="H265" t="s">
-        <v>527</v>
-      </c>
-      <c r="I265" t="s">
-        <v>528</v>
       </c>
       <c r="J265" t="s">
         <v>128</v>
@@ -12327,13 +12321,13 @@
         <v>13</v>
       </c>
       <c r="B266" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C266" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D266" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E266">
         <v>15</v>
@@ -12348,7 +12342,7 @@
         <v>152</v>
       </c>
       <c r="I266" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J266" t="s">
         <v>84</v>
@@ -12362,13 +12356,13 @@
         <v>13</v>
       </c>
       <c r="B267" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C267" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D267" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E267">
         <v>4</v>
@@ -12380,7 +12374,7 @@
         <v>81</v>
       </c>
       <c r="H267" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I267" t="s">
         <v>87</v>
@@ -12397,10 +12391,10 @@
         <v>13</v>
       </c>
       <c r="B268" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C268" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D268" t="s">
         <v>80</v>
@@ -12432,10 +12426,10 @@
         <v>13</v>
       </c>
       <c r="B269" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C269" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D269" t="s">
         <v>60</v>
@@ -12453,7 +12447,7 @@
         <v>95</v>
       </c>
       <c r="I269" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="J269" t="s">
         <v>97</v>
@@ -12467,10 +12461,10 @@
         <v>13</v>
       </c>
       <c r="B270" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C270" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D270" t="s">
         <v>108</v>
@@ -12502,10 +12496,10 @@
         <v>13</v>
       </c>
       <c r="B271" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C271" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D271" t="s">
         <v>71</v>
@@ -12537,13 +12531,13 @@
         <v>13</v>
       </c>
       <c r="B272" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C272" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D272" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E272">
         <v>4</v>
@@ -12572,13 +12566,13 @@
         <v>13</v>
       </c>
       <c r="B273" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C273" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D273" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E273">
         <v>4</v>
@@ -12590,7 +12584,7 @@
         <v>81</v>
       </c>
       <c r="H273" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I273" t="s">
         <v>87</v>
@@ -12607,10 +12601,10 @@
         <v>13</v>
       </c>
       <c r="B274" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C274" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D274" t="s">
         <v>156</v>
@@ -12628,7 +12622,7 @@
         <v>140</v>
       </c>
       <c r="I274" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="J274" t="s">
         <v>142</v>
@@ -12642,13 +12636,13 @@
         <v>13</v>
       </c>
       <c r="B275" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C275" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D275" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E275">
         <v>16</v>
@@ -12660,7 +12654,7 @@
         <v>81</v>
       </c>
       <c r="H275" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I275" t="s">
         <v>87</v>
@@ -12677,10 +12671,10 @@
         <v>13</v>
       </c>
       <c r="B276" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C276" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D276" t="s">
         <v>80</v>
@@ -12712,10 +12706,10 @@
         <v>13</v>
       </c>
       <c r="B277" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C277" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D277" t="s">
         <v>60</v>
@@ -12739,7 +12733,7 @@
         <v>18</v>
       </c>
       <c r="L277" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M277">
         <v>1</v>
@@ -12750,10 +12744,10 @@
         <v>13</v>
       </c>
       <c r="B278" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C278" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D278" t="s">
         <v>80</v>
@@ -12777,7 +12771,7 @@
         <v>18</v>
       </c>
       <c r="L278" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M278">
         <v>1</v>
@@ -12788,13 +12782,13 @@
         <v>13</v>
       </c>
       <c r="B279" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C279" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D279" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E279">
         <v>3</v>
@@ -12806,16 +12800,16 @@
         <v>18</v>
       </c>
       <c r="H279" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I279" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="J279" t="s">
         <v>18</v>
       </c>
       <c r="L279" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M279">
         <v>1</v>
@@ -12826,10 +12820,10 @@
         <v>13</v>
       </c>
       <c r="B280" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C280" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D280" t="s">
         <v>22</v>
@@ -12844,10 +12838,10 @@
         <v>18</v>
       </c>
       <c r="H280" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I280" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J280" t="s">
         <v>18</v>
@@ -12864,10 +12858,10 @@
         <v>13</v>
       </c>
       <c r="B281" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C281" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D281" t="s">
         <v>16</v>
@@ -12902,13 +12896,13 @@
         <v>13</v>
       </c>
       <c r="B282" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C282" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D282" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E282">
         <v>3</v>
@@ -12923,13 +12917,13 @@
         <v>82</v>
       </c>
       <c r="I282" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="J282" t="s">
         <v>18</v>
       </c>
       <c r="L282" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M282">
         <v>1</v>
@@ -12940,10 +12934,10 @@
         <v>13</v>
       </c>
       <c r="B283" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C283" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D283" t="s">
         <v>80</v>
@@ -12967,7 +12961,7 @@
         <v>18</v>
       </c>
       <c r="L283" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M283">
         <v>1</v>
@@ -12978,10 +12972,10 @@
         <v>13</v>
       </c>
       <c r="B284" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C284" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D284" t="s">
         <v>60</v>
@@ -12999,13 +12993,13 @@
         <v>95</v>
       </c>
       <c r="I284" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="J284" t="s">
         <v>18</v>
       </c>
       <c r="L284" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M284">
         <v>1</v>
@@ -13016,13 +13010,13 @@
         <v>13</v>
       </c>
       <c r="B285" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C285" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D285" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E285">
         <v>6</v>
@@ -13037,7 +13031,7 @@
         <v>18</v>
       </c>
       <c r="L285" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="M285">
         <v>1</v>
@@ -13048,13 +13042,13 @@
         <v>13</v>
       </c>
       <c r="B286" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C286" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D286" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E286">
         <v>8</v>
@@ -13069,7 +13063,7 @@
         <v>18</v>
       </c>
       <c r="L286" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M286">
         <v>1</v>
@@ -13080,10 +13074,10 @@
         <v>13</v>
       </c>
       <c r="B287" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C287" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D287" t="s">
         <v>16</v>
@@ -13118,10 +13112,10 @@
         <v>13</v>
       </c>
       <c r="B288" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C288" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D288" t="s">
         <v>22</v>
@@ -13136,10 +13130,10 @@
         <v>18</v>
       </c>
       <c r="H288" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I288" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J288" t="s">
         <v>18</v>
@@ -13156,10 +13150,10 @@
         <v>13</v>
       </c>
       <c r="B289" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C289" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D289" t="s">
         <v>60</v>
@@ -13177,13 +13171,13 @@
         <v>95</v>
       </c>
       <c r="I289" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="J289" t="s">
         <v>18</v>
       </c>
       <c r="L289" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M289">
         <v>1</v>
@@ -13194,10 +13188,10 @@
         <v>13</v>
       </c>
       <c r="B290" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C290" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D290" t="s">
         <v>56</v>
@@ -13215,7 +13209,7 @@
         <v>18</v>
       </c>
       <c r="L290" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M290">
         <v>1</v>
@@ -13226,13 +13220,13 @@
         <v>13</v>
       </c>
       <c r="B291" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C291" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D291" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E291">
         <v>8</v>
@@ -13247,7 +13241,7 @@
         <v>18</v>
       </c>
       <c r="L291" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M291">
         <v>1</v>
@@ -13258,13 +13252,13 @@
         <v>13</v>
       </c>
       <c r="B292" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C292" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D292" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="E292">
         <v>3</v>
@@ -13279,7 +13273,7 @@
         <v>18</v>
       </c>
       <c r="L292" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M292">
         <v>1</v>
@@ -13290,13 +13284,13 @@
         <v>13</v>
       </c>
       <c r="B293" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C293" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D293" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E293">
         <v>8</v>
@@ -13311,7 +13305,7 @@
         <v>18</v>
       </c>
       <c r="L293" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M293">
         <v>1</v>
@@ -13322,10 +13316,10 @@
         <v>13</v>
       </c>
       <c r="B294" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C294" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D294" t="s">
         <v>22</v>
@@ -13340,16 +13334,16 @@
         <v>18</v>
       </c>
       <c r="H294" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I294" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J294" t="s">
         <v>18</v>
       </c>
       <c r="K294" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="L294" t="s">
         <v>20</v>
@@ -13363,10 +13357,10 @@
         <v>13</v>
       </c>
       <c r="B295" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C295" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D295" t="s">
         <v>16</v>
@@ -13390,7 +13384,7 @@
         <v>18</v>
       </c>
       <c r="K295" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="L295" t="s">
         <v>20</v>
@@ -13404,10 +13398,10 @@
         <v>13</v>
       </c>
       <c r="B296" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C296" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D296" t="s">
         <v>80</v>
@@ -13431,7 +13425,7 @@
         <v>18</v>
       </c>
       <c r="L296" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M296">
         <v>1</v>
@@ -13442,10 +13436,10 @@
         <v>13</v>
       </c>
       <c r="B297" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C297" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D297" t="s">
         <v>16</v>
@@ -13469,7 +13463,7 @@
         <v>18</v>
       </c>
       <c r="L297" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M297">
         <v>1</v>
@@ -13480,10 +13474,10 @@
         <v>13</v>
       </c>
       <c r="B298" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C298" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D298" t="s">
         <v>23</v>
@@ -13501,7 +13495,7 @@
         <v>18</v>
       </c>
       <c r="L298" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M298">
         <v>1</v>
@@ -13512,10 +13506,10 @@
         <v>13</v>
       </c>
       <c r="B299" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C299" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D299" t="s">
         <v>22</v>
@@ -13533,7 +13527,7 @@
         <v>18</v>
       </c>
       <c r="L299" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M299">
         <v>1</v>
@@ -13544,13 +13538,13 @@
         <v>13</v>
       </c>
       <c r="B300" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C300" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D300" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E300">
         <v>6</v>
@@ -13565,7 +13559,7 @@
         <v>18</v>
       </c>
       <c r="L300" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M300">
         <v>1</v>
@@ -13576,10 +13570,10 @@
         <v>13</v>
       </c>
       <c r="B301" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C301" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D301" t="s">
         <v>108</v>
@@ -13597,7 +13591,7 @@
         <v>18</v>
       </c>
       <c r="L301" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M301">
         <v>1</v>
@@ -13608,13 +13602,13 @@
         <v>13</v>
       </c>
       <c r="B302" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C302" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D302" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E302">
         <v>6</v>
@@ -13629,7 +13623,7 @@
         <v>18</v>
       </c>
       <c r="L302" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M302">
         <v>1</v>
@@ -13640,13 +13634,13 @@
         <v>13</v>
       </c>
       <c r="B303" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C303" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D303" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E303">
         <v>5</v>
@@ -13661,7 +13655,7 @@
         <v>18</v>
       </c>
       <c r="L303" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M303">
         <v>1</v>
@@ -13672,10 +13666,10 @@
         <v>13</v>
       </c>
       <c r="B304" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C304" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D304" t="s">
         <v>80</v>
@@ -13699,7 +13693,7 @@
         <v>18</v>
       </c>
       <c r="L304" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M304">
         <v>1</v>
@@ -13710,13 +13704,13 @@
         <v>13</v>
       </c>
       <c r="B305" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C305" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D305" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E305">
         <v>6</v>
@@ -13731,13 +13725,13 @@
         <v>82</v>
       </c>
       <c r="I305" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="J305" t="s">
         <v>18</v>
       </c>
       <c r="L305" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M305">
         <v>1</v>
@@ -13748,10 +13742,10 @@
         <v>13</v>
       </c>
       <c r="B306" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C306" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D306" t="s">
         <v>16</v>
@@ -13775,7 +13769,7 @@
         <v>18</v>
       </c>
       <c r="L306" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M306">
         <v>1</v>
@@ -13786,13 +13780,13 @@
         <v>13</v>
       </c>
       <c r="B307" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C307" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D307" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E307">
         <v>7</v>
@@ -13813,7 +13807,7 @@
         <v>18</v>
       </c>
       <c r="L307" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M307">
         <v>1</v>
@@ -13824,10 +13818,10 @@
         <v>13</v>
       </c>
       <c r="B308" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C308" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D308" t="s">
         <v>35</v>
@@ -13845,13 +13839,13 @@
         <v>152</v>
       </c>
       <c r="I308" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J308" t="s">
         <v>18</v>
       </c>
       <c r="L308" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M308">
         <v>1</v>
@@ -13862,10 +13856,10 @@
         <v>13</v>
       </c>
       <c r="B309" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C309" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D309" t="s">
         <v>80</v>
@@ -13889,7 +13883,7 @@
         <v>18</v>
       </c>
       <c r="L309" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M309">
         <v>1</v>
@@ -13900,10 +13894,10 @@
         <v>13</v>
       </c>
       <c r="B310" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C310" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D310" t="s">
         <v>16</v>
@@ -13938,10 +13932,10 @@
         <v>13</v>
       </c>
       <c r="B311" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C311" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D311" t="s">
         <v>16</v>
@@ -13970,10 +13964,10 @@
         <v>13</v>
       </c>
       <c r="B312" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C312" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D312" t="s">
         <v>80</v>
@@ -13997,7 +13991,7 @@
         <v>18</v>
       </c>
       <c r="L312" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M312">
         <v>1</v>
@@ -14008,10 +14002,10 @@
         <v>13</v>
       </c>
       <c r="B313" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C313" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D313" t="s">
         <v>16</v>
@@ -14035,7 +14029,7 @@
         <v>18</v>
       </c>
       <c r="L313" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M313">
         <v>1</v>
@@ -14046,10 +14040,10 @@
         <v>13</v>
       </c>
       <c r="B314" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C314" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D314" t="s">
         <v>22</v>
@@ -14064,10 +14058,10 @@
         <v>18</v>
       </c>
       <c r="H314" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I314" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J314" t="s">
         <v>18</v>
@@ -14084,13 +14078,13 @@
         <v>13</v>
       </c>
       <c r="B315" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C315" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D315" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E315">
         <v>8</v>
@@ -14102,10 +14096,10 @@
         <v>18</v>
       </c>
       <c r="H315" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="I315" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="J315" t="s">
         <v>18</v>
@@ -14122,10 +14116,10 @@
         <v>13</v>
       </c>
       <c r="B316" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C316" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D316" t="s">
         <v>80</v>
@@ -14149,7 +14143,7 @@
         <v>18</v>
       </c>
       <c r="L316" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M316">
         <v>1</v>
@@ -14160,13 +14154,13 @@
         <v>13</v>
       </c>
       <c r="B317" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C317" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D317" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E317">
         <v>4</v>
@@ -14178,16 +14172,16 @@
         <v>18</v>
       </c>
       <c r="H317" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="I317" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="J317" t="s">
         <v>18</v>
       </c>
       <c r="L317" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="M317">
         <v>1</v>
@@ -14198,13 +14192,13 @@
         <v>13</v>
       </c>
       <c r="B318" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C318" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D318" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E318">
         <v>4</v>
@@ -14216,16 +14210,16 @@
         <v>18</v>
       </c>
       <c r="H318" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I318" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J318" t="s">
         <v>18</v>
       </c>
       <c r="L318" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M318">
         <v>1</v>
@@ -14236,10 +14230,10 @@
         <v>13</v>
       </c>
       <c r="B319" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C319" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D319" t="s">
         <v>16</v>
@@ -14274,10 +14268,10 @@
         <v>13</v>
       </c>
       <c r="B320" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C320" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D320" t="s">
         <v>80</v>
@@ -14301,7 +14295,7 @@
         <v>18</v>
       </c>
       <c r="L320" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M320">
         <v>1</v>
@@ -14312,10 +14306,10 @@
         <v>13</v>
       </c>
       <c r="B321" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C321" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D321" t="s">
         <v>22</v>
@@ -14330,10 +14324,10 @@
         <v>18</v>
       </c>
       <c r="H321" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I321" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J321" t="s">
         <v>18</v>
@@ -14350,13 +14344,13 @@
         <v>13</v>
       </c>
       <c r="B322" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C322" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D322" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E322">
         <v>3</v>
@@ -14368,10 +14362,10 @@
         <v>18</v>
       </c>
       <c r="H322" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="I322" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="J322" t="s">
         <v>18</v>
@@ -14388,10 +14382,10 @@
         <v>13</v>
       </c>
       <c r="B323" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C323" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D323" t="s">
         <v>80</v>
@@ -14423,13 +14417,13 @@
         <v>13</v>
       </c>
       <c r="B324" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C324" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D324" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E324">
         <v>4</v>
@@ -14441,7 +14435,7 @@
         <v>81</v>
       </c>
       <c r="H324" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I324" t="s">
         <v>87</v>
@@ -14458,10 +14452,10 @@
         <v>13</v>
       </c>
       <c r="B325" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C325" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="D325" t="s">
         <v>60</v>
@@ -14479,7 +14473,7 @@
         <v>95</v>
       </c>
       <c r="I325" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="J325" t="s">
         <v>97</v>
@@ -14493,10 +14487,10 @@
         <v>13</v>
       </c>
       <c r="B326" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C326" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="D326" t="s">
         <v>16</v>
@@ -14528,10 +14522,10 @@
         <v>13</v>
       </c>
       <c r="B327" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C327" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="D327" t="s">
         <v>71</v>
@@ -14563,10 +14557,10 @@
         <v>13</v>
       </c>
       <c r="B328" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C328" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="D328" t="s">
         <v>80</v>
@@ -14590,7 +14584,7 @@
         <v>18</v>
       </c>
       <c r="L328" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M328">
         <v>1</v>
@@ -14601,10 +14595,10 @@
         <v>13</v>
       </c>
       <c r="B329" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C329" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D329" t="s">
         <v>16</v>
@@ -14639,13 +14633,13 @@
         <v>13</v>
       </c>
       <c r="B330" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C330" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D330" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E330">
         <v>17</v>
@@ -14657,7 +14651,7 @@
         <v>18</v>
       </c>
       <c r="H330" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I330" t="s">
         <v>136</v>
@@ -14666,7 +14660,7 @@
         <v>18</v>
       </c>
       <c r="L330" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M330">
         <v>1</v>
@@ -14677,10 +14671,10 @@
         <v>13</v>
       </c>
       <c r="B331" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C331" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="D331" t="s">
         <v>80</v>
@@ -14704,7 +14698,7 @@
         <v>18</v>
       </c>
       <c r="L331" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M331">
         <v>1</v>
@@ -14715,13 +14709,13 @@
         <v>13</v>
       </c>
       <c r="B332" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C332" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D332" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E332">
         <v>10</v>
@@ -14736,7 +14730,7 @@
         <v>18</v>
       </c>
       <c r="L332" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M332">
         <v>1</v>
@@ -14747,10 +14741,10 @@
         <v>13</v>
       </c>
       <c r="B333" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C333" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D333" t="s">
         <v>45</v>
@@ -14768,7 +14762,7 @@
         <v>18</v>
       </c>
       <c r="L333" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M333">
         <v>1</v>
@@ -14779,10 +14773,10 @@
         <v>13</v>
       </c>
       <c r="B334" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C334" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D334" t="s">
         <v>60</v>
@@ -14806,7 +14800,7 @@
         <v>18</v>
       </c>
       <c r="L334" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M334">
         <v>1</v>
@@ -14817,13 +14811,13 @@
         <v>13</v>
       </c>
       <c r="B335" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C335" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D335" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E335">
         <v>3</v>
@@ -14835,16 +14829,16 @@
         <v>18</v>
       </c>
       <c r="H335" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I335" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J335" t="s">
         <v>18</v>
       </c>
       <c r="L335" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M335">
         <v>1</v>
@@ -14855,10 +14849,10 @@
         <v>13</v>
       </c>
       <c r="B336" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C336" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D336" t="s">
         <v>16</v>
@@ -14882,7 +14876,7 @@
         <v>18</v>
       </c>
       <c r="L336" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M336">
         <v>1</v>
@@ -14893,10 +14887,10 @@
         <v>13</v>
       </c>
       <c r="B337" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C337" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D337" t="s">
         <v>108</v>
@@ -14920,7 +14914,7 @@
         <v>18</v>
       </c>
       <c r="L337" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M337">
         <v>1</v>
@@ -14931,13 +14925,13 @@
         <v>13</v>
       </c>
       <c r="B338" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C338" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D338" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E338">
         <v>5</v>
@@ -14949,7 +14943,7 @@
         <v>81</v>
       </c>
       <c r="H338" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I338" t="s">
         <v>87</v>
@@ -14966,10 +14960,10 @@
         <v>13</v>
       </c>
       <c r="B339" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C339" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D339" t="s">
         <v>108</v>
@@ -15001,10 +14995,10 @@
         <v>13</v>
       </c>
       <c r="B340" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C340" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="D340" t="s">
         <v>114</v>
@@ -15019,7 +15013,7 @@
         <v>81</v>
       </c>
       <c r="H340" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I340" t="s">
         <v>87</v>
@@ -15036,10 +15030,10 @@
         <v>13</v>
       </c>
       <c r="B341" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C341" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="D341" t="s">
         <v>80</v>
@@ -15071,10 +15065,10 @@
         <v>13</v>
       </c>
       <c r="B342" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C342" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D342" t="s">
         <v>80</v>
@@ -15106,10 +15100,10 @@
         <v>13</v>
       </c>
       <c r="B343" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C343" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="D343" t="s">
         <v>60</v>
@@ -15127,7 +15121,7 @@
         <v>95</v>
       </c>
       <c r="I343" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="J343" t="s">
         <v>97</v>
@@ -15141,10 +15135,10 @@
         <v>13</v>
       </c>
       <c r="B344" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="C344" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D344" t="s">
         <v>63</v>
@@ -15176,10 +15170,10 @@
         <v>13</v>
       </c>
       <c r="B345" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C345" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="D345" t="s">
         <v>45</v>
@@ -15211,13 +15205,13 @@
         <v>13</v>
       </c>
       <c r="B346" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C346" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D346" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E346">
         <v>4</v>
@@ -15229,7 +15223,7 @@
         <v>81</v>
       </c>
       <c r="H346" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I346" t="s">
         <v>87</v>
@@ -15246,10 +15240,10 @@
         <v>13</v>
       </c>
       <c r="B347" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C347" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D347" t="s">
         <v>80</v>
@@ -15281,10 +15275,10 @@
         <v>13</v>
       </c>
       <c r="B348" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C348" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D348" t="s">
         <v>16</v>
@@ -15316,10 +15310,10 @@
         <v>13</v>
       </c>
       <c r="B349" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C349" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D349" t="s">
         <v>45</v>
@@ -15351,13 +15345,13 @@
         <v>13</v>
       </c>
       <c r="B350" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C350" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D350" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E350">
         <v>4</v>
@@ -15369,10 +15363,10 @@
         <v>81</v>
       </c>
       <c r="H350" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I350" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="J350" t="s">
         <v>97</v>
@@ -15386,13 +15380,13 @@
         <v>13</v>
       </c>
       <c r="B351" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="C351" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D351" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E351">
         <v>4</v>
@@ -15404,7 +15398,7 @@
         <v>81</v>
       </c>
       <c r="H351" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I351" t="s">
         <v>87</v>
@@ -15421,10 +15415,10 @@
         <v>13</v>
       </c>
       <c r="B352" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C352" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D352" t="s">
         <v>80</v>
@@ -15456,13 +15450,13 @@
         <v>13</v>
       </c>
       <c r="B353" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C353" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D353" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E353">
         <v>19</v>
@@ -15474,10 +15468,10 @@
         <v>81</v>
       </c>
       <c r="H353" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I353" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J353" t="s">
         <v>97</v>
@@ -15491,10 +15485,10 @@
         <v>13</v>
       </c>
       <c r="B354" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C354" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="D354" t="s">
         <v>16</v>
@@ -15526,10 +15520,10 @@
         <v>13</v>
       </c>
       <c r="B355" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C355" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="D355" t="s">
         <v>80</v>
@@ -15561,10 +15555,10 @@
         <v>13</v>
       </c>
       <c r="B356" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C356" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D356" t="s">
         <v>60</v>
@@ -15582,7 +15576,7 @@
         <v>95</v>
       </c>
       <c r="I356" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="J356" t="s">
         <v>97</v>
@@ -15596,10 +15590,10 @@
         <v>13</v>
       </c>
       <c r="B357" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C357" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D357" t="s">
         <v>151</v>
@@ -15631,10 +15625,10 @@
         <v>13</v>
       </c>
       <c r="B358" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C358" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D358" t="s">
         <v>156</v>
@@ -15666,10 +15660,10 @@
         <v>13</v>
       </c>
       <c r="B359" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C359" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D359" t="s">
         <v>160</v>
@@ -15684,13 +15678,13 @@
         <v>81</v>
       </c>
       <c r="H359" t="s">
+        <v>986</v>
+      </c>
+      <c r="I359" t="s">
         <v>161</v>
       </c>
-      <c r="I359" t="s">
-        <v>162</v>
-      </c>
       <c r="J359" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="M359">
         <v>1</v>
@@ -15701,13 +15695,13 @@
         <v>13</v>
       </c>
       <c r="B360" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C360" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="D360" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E360">
         <v>4</v>
@@ -15719,7 +15713,7 @@
         <v>81</v>
       </c>
       <c r="H360" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I360" t="s">
         <v>87</v>
@@ -15736,13 +15730,13 @@
         <v>13</v>
       </c>
       <c r="B361" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C361" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D361" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E361">
         <v>6</v>
@@ -15771,10 +15765,10 @@
         <v>13</v>
       </c>
       <c r="B362" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C362" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D362" t="s">
         <v>45</v>
@@ -15806,10 +15800,10 @@
         <v>13</v>
       </c>
       <c r="B363" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C363" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D363" t="s">
         <v>80</v>
@@ -15841,10 +15835,10 @@
         <v>13</v>
       </c>
       <c r="B364" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C364" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D364" t="s">
         <v>80</v>
@@ -15876,10 +15870,10 @@
         <v>13</v>
       </c>
       <c r="B365" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C365" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D365" t="s">
         <v>60</v>
@@ -15897,7 +15891,7 @@
         <v>95</v>
       </c>
       <c r="I365" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="J365" t="s">
         <v>97</v>
@@ -15911,31 +15905,31 @@
         <v>13</v>
       </c>
       <c r="B366" t="s">
+        <v>711</v>
+      </c>
+      <c r="C366" t="s">
+        <v>712</v>
+      </c>
+      <c r="D366" t="s">
+        <v>190</v>
+      </c>
+      <c r="E366">
+        <v>13</v>
+      </c>
+      <c r="F366" t="s">
+        <v>17</v>
+      </c>
+      <c r="G366" t="s">
+        <v>81</v>
+      </c>
+      <c r="H366" t="s">
+        <v>713</v>
+      </c>
+      <c r="I366" t="s">
         <v>714</v>
       </c>
-      <c r="C366" t="s">
+      <c r="J366" t="s">
         <v>715</v>
-      </c>
-      <c r="D366" t="s">
-        <v>192</v>
-      </c>
-      <c r="E366">
-        <v>13</v>
-      </c>
-      <c r="F366" t="s">
-        <v>17</v>
-      </c>
-      <c r="G366" t="s">
-        <v>81</v>
-      </c>
-      <c r="H366" t="s">
-        <v>716</v>
-      </c>
-      <c r="I366" t="s">
-        <v>717</v>
-      </c>
-      <c r="J366" t="s">
-        <v>718</v>
       </c>
       <c r="M366">
         <v>1</v>
@@ -15946,10 +15940,10 @@
         <v>13</v>
       </c>
       <c r="B367" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C367" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D367" t="s">
         <v>71</v>
@@ -15981,13 +15975,13 @@
         <v>13</v>
       </c>
       <c r="B368" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C368" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D368" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E368">
         <v>2</v>
@@ -16016,13 +16010,13 @@
         <v>13</v>
       </c>
       <c r="B369" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="C369" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D369" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E369">
         <v>4</v>
@@ -16034,7 +16028,7 @@
         <v>81</v>
       </c>
       <c r="H369" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I369" t="s">
         <v>87</v>
@@ -16051,10 +16045,10 @@
         <v>13</v>
       </c>
       <c r="B370" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C370" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D370" t="s">
         <v>63</v>
@@ -16086,10 +16080,10 @@
         <v>13</v>
       </c>
       <c r="B371" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C371" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D371" t="s">
         <v>139</v>
@@ -16121,10 +16115,10 @@
         <v>13</v>
       </c>
       <c r="B372" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C372" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D372" t="s">
         <v>80</v>
@@ -16156,10 +16150,10 @@
         <v>13</v>
       </c>
       <c r="B373" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C373" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D373" t="s">
         <v>80</v>
@@ -16177,7 +16171,7 @@
         <v>18</v>
       </c>
       <c r="L373" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M373">
         <v>1</v>
@@ -16188,10 +16182,10 @@
         <v>13</v>
       </c>
       <c r="B374" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C374" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D374" t="s">
         <v>80</v>
@@ -16215,7 +16209,7 @@
         <v>18</v>
       </c>
       <c r="L374" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M374">
         <v>1</v>
@@ -16226,10 +16220,10 @@
         <v>13</v>
       </c>
       <c r="B375" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C375" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D375" t="s">
         <v>92</v>
@@ -16247,7 +16241,7 @@
         <v>18</v>
       </c>
       <c r="L375" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M375">
         <v>1</v>
@@ -16258,10 +16252,10 @@
         <v>13</v>
       </c>
       <c r="B376" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C376" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D376" t="s">
         <v>80</v>
@@ -16285,7 +16279,7 @@
         <v>18</v>
       </c>
       <c r="L376" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M376">
         <v>1</v>
@@ -16296,10 +16290,10 @@
         <v>13</v>
       </c>
       <c r="B377" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C377" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D377" t="s">
         <v>22</v>
@@ -16328,10 +16322,10 @@
         <v>13</v>
       </c>
       <c r="B378" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C378" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D378" t="s">
         <v>92</v>
@@ -16349,7 +16343,7 @@
         <v>18</v>
       </c>
       <c r="L378" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M378">
         <v>1</v>
@@ -16360,13 +16354,13 @@
         <v>13</v>
       </c>
       <c r="B379" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C379" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D379" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E379">
         <v>3</v>
@@ -16381,7 +16375,7 @@
         <v>18</v>
       </c>
       <c r="L379" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M379">
         <v>1</v>
@@ -16392,10 +16386,10 @@
         <v>13</v>
       </c>
       <c r="B380" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C380" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D380" t="s">
         <v>45</v>
@@ -16413,7 +16407,7 @@
         <v>18</v>
       </c>
       <c r="L380" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M380">
         <v>1</v>
@@ -16424,10 +16418,10 @@
         <v>13</v>
       </c>
       <c r="B381" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C381" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D381" t="s">
         <v>22</v>
@@ -16456,13 +16450,13 @@
         <v>13</v>
       </c>
       <c r="B382" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C382" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D382" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E382">
         <v>14</v>
@@ -16488,10 +16482,10 @@
         <v>13</v>
       </c>
       <c r="B383" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C383" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D383" t="s">
         <v>80</v>
@@ -16509,7 +16503,7 @@
         <v>18</v>
       </c>
       <c r="L383" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M383">
         <v>1</v>
@@ -16520,10 +16514,10 @@
         <v>13</v>
       </c>
       <c r="B384" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="C384" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="D384" t="s">
         <v>16</v>
@@ -16552,10 +16546,10 @@
         <v>13</v>
       </c>
       <c r="B385" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C385" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D385" t="s">
         <v>80</v>
@@ -16573,7 +16567,7 @@
         <v>18</v>
       </c>
       <c r="L385" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M385">
         <v>1</v>
@@ -16584,13 +16578,13 @@
         <v>13</v>
       </c>
       <c r="B386" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C386" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="D386" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E386">
         <v>5</v>
@@ -16616,10 +16610,10 @@
         <v>13</v>
       </c>
       <c r="B387" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="C387" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="D387" t="s">
         <v>92</v>
@@ -16637,7 +16631,7 @@
         <v>18</v>
       </c>
       <c r="L387" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M387">
         <v>1</v>
@@ -16648,13 +16642,13 @@
         <v>13</v>
       </c>
       <c r="B388" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C388" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D388" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E388">
         <v>4</v>
@@ -16669,7 +16663,7 @@
         <v>18</v>
       </c>
       <c r="L388" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M388">
         <v>1</v>
@@ -16680,10 +16674,10 @@
         <v>13</v>
       </c>
       <c r="B389" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C389" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D389" t="s">
         <v>45</v>
@@ -16701,7 +16695,7 @@
         <v>18</v>
       </c>
       <c r="L389" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M389">
         <v>1</v>
@@ -16712,10 +16706,10 @@
         <v>13</v>
       </c>
       <c r="B390" t="s">
+        <v>750</v>
+      </c>
+      <c r="C390" t="s">
         <v>753</v>
-      </c>
-      <c r="C390" t="s">
-        <v>756</v>
       </c>
       <c r="D390" t="s">
         <v>80</v>
@@ -16733,7 +16727,7 @@
         <v>18</v>
       </c>
       <c r="L390" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M390">
         <v>1</v>
@@ -16744,10 +16738,10 @@
         <v>13</v>
       </c>
       <c r="B391" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C391" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D391" t="s">
         <v>80</v>
@@ -16771,7 +16765,7 @@
         <v>18</v>
       </c>
       <c r="L391" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M391">
         <v>1</v>
@@ -16782,10 +16776,10 @@
         <v>13</v>
       </c>
       <c r="B392" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="C392" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D392" t="s">
         <v>45</v>
@@ -16809,7 +16803,7 @@
         <v>18</v>
       </c>
       <c r="L392" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M392">
         <v>1</v>
@@ -16820,10 +16814,10 @@
         <v>13</v>
       </c>
       <c r="B393" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C393" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D393" t="s">
         <v>80</v>
@@ -16841,7 +16835,7 @@
         <v>18</v>
       </c>
       <c r="L393" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M393">
         <v>1</v>
@@ -16852,10 +16846,10 @@
         <v>13</v>
       </c>
       <c r="B394" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C394" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D394" t="s">
         <v>80</v>
@@ -16879,7 +16873,7 @@
         <v>18</v>
       </c>
       <c r="L394" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M394">
         <v>1</v>
@@ -16890,13 +16884,13 @@
         <v>13</v>
       </c>
       <c r="B395" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C395" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D395" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E395">
         <v>3</v>
@@ -16922,10 +16916,10 @@
         <v>13</v>
       </c>
       <c r="B396" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C396" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D396" t="s">
         <v>80</v>
@@ -16943,7 +16937,7 @@
         <v>18</v>
       </c>
       <c r="L396" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M396">
         <v>1</v>
@@ -16954,10 +16948,10 @@
         <v>13</v>
       </c>
       <c r="B397" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C397" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D397" t="s">
         <v>22</v>
@@ -16986,10 +16980,10 @@
         <v>13</v>
       </c>
       <c r="B398" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C398" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D398" t="s">
         <v>45</v>
@@ -17013,7 +17007,7 @@
         <v>18</v>
       </c>
       <c r="L398" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M398">
         <v>1</v>
@@ -17024,10 +17018,10 @@
         <v>13</v>
       </c>
       <c r="B399" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C399" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D399" t="s">
         <v>108</v>
@@ -17045,7 +17039,7 @@
         <v>18</v>
       </c>
       <c r="L399" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M399">
         <v>1</v>
@@ -17056,13 +17050,13 @@
         <v>13</v>
       </c>
       <c r="B400" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C400" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="D400" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E400">
         <v>6</v>
@@ -17074,7 +17068,7 @@
         <v>18</v>
       </c>
       <c r="H400" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I400" t="s">
         <v>87</v>
@@ -17083,7 +17077,7 @@
         <v>18</v>
       </c>
       <c r="L400" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M400">
         <v>1</v>
@@ -17094,13 +17088,13 @@
         <v>13</v>
       </c>
       <c r="B401" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C401" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="D401" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E401">
         <v>7</v>
@@ -17112,16 +17106,16 @@
         <v>18</v>
       </c>
       <c r="H401" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="I401" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="J401" t="s">
         <v>18</v>
       </c>
       <c r="L401" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M401">
         <v>1</v>
@@ -17132,13 +17126,13 @@
         <v>13</v>
       </c>
       <c r="B402" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="C402" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="D402" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E402">
         <v>4</v>
@@ -17153,7 +17147,7 @@
         <v>18</v>
       </c>
       <c r="L402" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M402">
         <v>1</v>
@@ -17164,10 +17158,10 @@
         <v>13</v>
       </c>
       <c r="B403" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C403" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D403" t="s">
         <v>22</v>
@@ -17182,10 +17176,10 @@
         <v>18</v>
       </c>
       <c r="H403" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I403" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J403" t="s">
         <v>18</v>
@@ -17202,13 +17196,13 @@
         <v>13</v>
       </c>
       <c r="B404" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C404" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D404" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E404">
         <v>6</v>
@@ -17223,7 +17217,7 @@
         <v>18</v>
       </c>
       <c r="L404" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M404">
         <v>1</v>
@@ -17234,10 +17228,10 @@
         <v>13</v>
       </c>
       <c r="B405" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C405" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D405" t="s">
         <v>60</v>
@@ -17261,7 +17255,7 @@
         <v>18</v>
       </c>
       <c r="L405" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M405">
         <v>1</v>
@@ -17272,10 +17266,10 @@
         <v>13</v>
       </c>
       <c r="B406" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C406" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="D406" t="s">
         <v>156</v>
@@ -17293,7 +17287,7 @@
         <v>18</v>
       </c>
       <c r="L406" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M406">
         <v>1</v>
@@ -17304,10 +17298,10 @@
         <v>13</v>
       </c>
       <c r="B407" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C407" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D407" t="s">
         <v>80</v>
@@ -17331,7 +17325,7 @@
         <v>18</v>
       </c>
       <c r="L407" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M407">
         <v>1</v>
@@ -17342,10 +17336,10 @@
         <v>13</v>
       </c>
       <c r="B408" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C408" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D408" t="s">
         <v>22</v>
@@ -17360,10 +17354,10 @@
         <v>18</v>
       </c>
       <c r="H408" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I408" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J408" t="s">
         <v>18</v>
@@ -17380,13 +17374,13 @@
         <v>13</v>
       </c>
       <c r="B409" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="C409" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D409" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E409">
         <v>4</v>
@@ -17398,7 +17392,7 @@
         <v>18</v>
       </c>
       <c r="H409" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I409" t="s">
         <v>87</v>
@@ -17407,7 +17401,7 @@
         <v>18</v>
       </c>
       <c r="L409" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M409">
         <v>1</v>
@@ -17418,10 +17412,10 @@
         <v>13</v>
       </c>
       <c r="B410" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C410" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D410" t="s">
         <v>45</v>
@@ -17445,7 +17439,7 @@
         <v>18</v>
       </c>
       <c r="L410" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M410">
         <v>1</v>
@@ -17456,10 +17450,10 @@
         <v>13</v>
       </c>
       <c r="B411" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C411" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D411" t="s">
         <v>80</v>
@@ -17491,10 +17485,10 @@
         <v>13</v>
       </c>
       <c r="B412" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C412" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="D412" t="s">
         <v>60</v>
@@ -17526,10 +17520,10 @@
         <v>13</v>
       </c>
       <c r="B413" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C413" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D413" t="s">
         <v>108</v>
@@ -17561,10 +17555,10 @@
         <v>13</v>
       </c>
       <c r="B414" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C414" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="D414" t="s">
         <v>160</v>
@@ -17579,13 +17573,13 @@
         <v>81</v>
       </c>
       <c r="H414" t="s">
+        <v>986</v>
+      </c>
+      <c r="I414" t="s">
         <v>161</v>
       </c>
-      <c r="I414" t="s">
-        <v>162</v>
-      </c>
       <c r="J414" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="M414">
         <v>1</v>
@@ -17596,10 +17590,10 @@
         <v>13</v>
       </c>
       <c r="B415" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="C415" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="D415" t="s">
         <v>35</v>
@@ -17617,7 +17611,7 @@
         <v>152</v>
       </c>
       <c r="I415" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J415" t="s">
         <v>84</v>
@@ -17631,10 +17625,10 @@
         <v>13</v>
       </c>
       <c r="B416" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="C416" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="D416" t="s">
         <v>22</v>
@@ -17649,10 +17643,10 @@
         <v>18</v>
       </c>
       <c r="H416" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I416" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J416" t="s">
         <v>18</v>
@@ -17669,13 +17663,13 @@
         <v>13</v>
       </c>
       <c r="B417" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C417" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D417" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="E417">
         <v>8</v>
@@ -17690,7 +17684,7 @@
         <v>18</v>
       </c>
       <c r="L417" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M417">
         <v>1</v>
@@ -17701,13 +17695,13 @@
         <v>13</v>
       </c>
       <c r="B418" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="C418" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="D418" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E418">
         <v>7</v>
@@ -17719,7 +17713,7 @@
         <v>81</v>
       </c>
       <c r="H418" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I418" t="s">
         <v>87</v>
@@ -17736,10 +17730,10 @@
         <v>13</v>
       </c>
       <c r="B419" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C419" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="D419" t="s">
         <v>16</v>
@@ -17771,10 +17765,10 @@
         <v>13</v>
       </c>
       <c r="B420" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C420" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="D420" t="s">
         <v>80</v>
@@ -17806,13 +17800,13 @@
         <v>13</v>
       </c>
       <c r="B421" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C421" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D421" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E421">
         <v>5</v>
@@ -17824,10 +17818,10 @@
         <v>18</v>
       </c>
       <c r="H421" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I421" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J421" t="s">
         <v>18</v>
@@ -17841,13 +17835,13 @@
         <v>13</v>
       </c>
       <c r="B422" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C422" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="D422" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E422">
         <v>4</v>
@@ -17859,7 +17853,7 @@
         <v>81</v>
       </c>
       <c r="H422" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I422" t="s">
         <v>87</v>
@@ -17876,10 +17870,10 @@
         <v>13</v>
       </c>
       <c r="B423" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="C423" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="D423" t="s">
         <v>80</v>
@@ -17911,13 +17905,13 @@
         <v>13</v>
       </c>
       <c r="B424" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="C424" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D424" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E424">
         <v>4</v>
@@ -17946,10 +17940,10 @@
         <v>13</v>
       </c>
       <c r="B425" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="C425" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="D425" t="s">
         <v>156</v>
@@ -17967,7 +17961,7 @@
         <v>140</v>
       </c>
       <c r="I425" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="J425" t="s">
         <v>142</v>
@@ -17981,13 +17975,13 @@
         <v>13</v>
       </c>
       <c r="B426" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="C426" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="D426" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E426">
         <v>6</v>
@@ -17999,10 +17993,10 @@
         <v>81</v>
       </c>
       <c r="H426" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I426" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="J426" t="s">
         <v>142</v>
@@ -18016,13 +18010,13 @@
         <v>13</v>
       </c>
       <c r="B427" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="C427" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="D427" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E427">
         <v>8</v>
@@ -18034,10 +18028,10 @@
         <v>81</v>
       </c>
       <c r="H427" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I427" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="J427" t="s">
         <v>84</v>
@@ -18051,10 +18045,10 @@
         <v>13</v>
       </c>
       <c r="B428" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C428" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="D428" t="s">
         <v>16</v>
@@ -18086,10 +18080,10 @@
         <v>13</v>
       </c>
       <c r="B429" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="C429" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="D429" t="s">
         <v>80</v>
@@ -18121,10 +18115,10 @@
         <v>13</v>
       </c>
       <c r="B430" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C430" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="D430" t="s">
         <v>45</v>
@@ -18156,10 +18150,10 @@
         <v>13</v>
       </c>
       <c r="B431" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C431" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="D431" t="s">
         <v>71</v>
@@ -18191,13 +18185,13 @@
         <v>13</v>
       </c>
       <c r="B432" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C432" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="D432" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E432">
         <v>4</v>
@@ -18209,7 +18203,7 @@
         <v>81</v>
       </c>
       <c r="H432" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I432" t="s">
         <v>87</v>
@@ -18226,10 +18220,10 @@
         <v>13</v>
       </c>
       <c r="B433" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C433" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="D433" t="s">
         <v>80</v>
@@ -18261,10 +18255,10 @@
         <v>13</v>
       </c>
       <c r="B434" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C434" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="D434" t="s">
         <v>60</v>
@@ -18296,13 +18290,13 @@
         <v>13</v>
       </c>
       <c r="B435" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="C435" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="D435" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E435">
         <v>3</v>
@@ -18331,13 +18325,13 @@
         <v>13</v>
       </c>
       <c r="B436" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="C436" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="D436" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E436">
         <v>9</v>
@@ -18352,7 +18346,7 @@
         <v>109</v>
       </c>
       <c r="I436" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J436" t="s">
         <v>111</v>
@@ -18366,10 +18360,10 @@
         <v>13</v>
       </c>
       <c r="B437" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="C437" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="D437" t="s">
         <v>80</v>
@@ -18401,10 +18395,10 @@
         <v>13</v>
       </c>
       <c r="B438" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C438" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="D438" t="s">
         <v>80</v>
@@ -18428,7 +18422,7 @@
         <v>18</v>
       </c>
       <c r="L438" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M438">
         <v>1</v>
@@ -18439,10 +18433,10 @@
         <v>13</v>
       </c>
       <c r="B439" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C439" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="D439" t="s">
         <v>16</v>
@@ -18477,10 +18471,10 @@
         <v>13</v>
       </c>
       <c r="B440" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C440" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D440" t="s">
         <v>22</v>
@@ -18495,10 +18489,10 @@
         <v>18</v>
       </c>
       <c r="H440" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I440" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J440" t="s">
         <v>18</v>
@@ -18515,10 +18509,10 @@
         <v>13</v>
       </c>
       <c r="B441" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C441" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D441" t="s">
         <v>80</v>
@@ -18542,7 +18536,7 @@
         <v>18</v>
       </c>
       <c r="L441" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M441">
         <v>1</v>
@@ -18553,10 +18547,10 @@
         <v>13</v>
       </c>
       <c r="B442" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C442" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="D442" t="s">
         <v>22</v>
@@ -18571,10 +18565,10 @@
         <v>18</v>
       </c>
       <c r="H442" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I442" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J442" t="s">
         <v>18</v>
@@ -18591,10 +18585,10 @@
         <v>13</v>
       </c>
       <c r="B443" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C443" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="D443" t="s">
         <v>80</v>
@@ -18612,7 +18606,7 @@
         <v>18</v>
       </c>
       <c r="L443" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M443">
         <v>1</v>
@@ -18623,10 +18617,10 @@
         <v>13</v>
       </c>
       <c r="B444" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="C444" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="D444" t="s">
         <v>22</v>
@@ -18641,10 +18635,10 @@
         <v>18</v>
       </c>
       <c r="H444" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I444" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J444" t="s">
         <v>18</v>
@@ -18661,13 +18655,13 @@
         <v>13</v>
       </c>
       <c r="B445" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="C445" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="D445" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E445">
         <v>5</v>
@@ -18679,7 +18673,7 @@
         <v>81</v>
       </c>
       <c r="H445" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I445" t="s">
         <v>87</v>
@@ -18696,10 +18690,10 @@
         <v>13</v>
       </c>
       <c r="B446" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="C446" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="D446" t="s">
         <v>63</v>
@@ -18731,10 +18725,10 @@
         <v>13</v>
       </c>
       <c r="B447" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="C447" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="D447" t="s">
         <v>151</v>
@@ -18766,10 +18760,10 @@
         <v>13</v>
       </c>
       <c r="B448" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="C448" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="D448" t="s">
         <v>156</v>
@@ -18787,7 +18781,7 @@
         <v>140</v>
       </c>
       <c r="I448" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="J448" t="s">
         <v>142</v>
@@ -18801,10 +18795,10 @@
         <v>13</v>
       </c>
       <c r="B449" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="C449" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D449" t="s">
         <v>16</v>
@@ -18836,10 +18830,10 @@
         <v>13</v>
       </c>
       <c r="B450" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C450" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="D450" t="s">
         <v>80</v>
@@ -18871,10 +18865,10 @@
         <v>13</v>
       </c>
       <c r="B451" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="C451" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="D451" t="s">
         <v>80</v>
@@ -18906,10 +18900,10 @@
         <v>13</v>
       </c>
       <c r="B452" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C452" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="D452" t="s">
         <v>60</v>
@@ -18941,13 +18935,13 @@
         <v>13</v>
       </c>
       <c r="B453" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="C453" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="D453" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E453">
         <v>10</v>
@@ -18959,10 +18953,10 @@
         <v>81</v>
       </c>
       <c r="H453" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I453" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="J453" t="s">
         <v>88</v>
@@ -18976,10 +18970,10 @@
         <v>13</v>
       </c>
       <c r="B454" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C454" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="D454" t="s">
         <v>45</v>
@@ -19011,13 +19005,13 @@
         <v>13</v>
       </c>
       <c r="B455" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="C455" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="D455" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E455">
         <v>2</v>
@@ -19046,13 +19040,13 @@
         <v>13</v>
       </c>
       <c r="B456" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="C456" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="D456" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E456">
         <v>4</v>
@@ -19064,7 +19058,7 @@
         <v>81</v>
       </c>
       <c r="H456" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I456" t="s">
         <v>87</v>
@@ -19081,13 +19075,13 @@
         <v>13</v>
       </c>
       <c r="B457" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="C457" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="D457" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E457">
         <v>6</v>
@@ -19116,10 +19110,10 @@
         <v>13</v>
       </c>
       <c r="B458" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="C458" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D458" t="s">
         <v>63</v>
@@ -19151,10 +19145,10 @@
         <v>13</v>
       </c>
       <c r="B459" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C459" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="D459" t="s">
         <v>160</v>
@@ -19169,13 +19163,13 @@
         <v>81</v>
       </c>
       <c r="H459" t="s">
+        <v>986</v>
+      </c>
+      <c r="I459" t="s">
         <v>161</v>
       </c>
-      <c r="I459" t="s">
-        <v>162</v>
-      </c>
       <c r="J459" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="M459">
         <v>1</v>
@@ -19186,10 +19180,10 @@
         <v>13</v>
       </c>
       <c r="B460" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C460" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D460" t="s">
         <v>80</v>
@@ -19221,13 +19215,13 @@
         <v>13</v>
       </c>
       <c r="B461" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="C461" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="D461" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E461">
         <v>2</v>
@@ -19256,13 +19250,13 @@
         <v>13</v>
       </c>
       <c r="B462" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C462" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="D462" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E462">
         <v>5</v>
@@ -19274,7 +19268,7 @@
         <v>81</v>
       </c>
       <c r="H462" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I462" t="s">
         <v>87</v>
@@ -19291,13 +19285,13 @@
         <v>13</v>
       </c>
       <c r="B463" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="C463" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="D463" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E463">
         <v>6</v>
@@ -19326,10 +19320,10 @@
         <v>13</v>
       </c>
       <c r="B464" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="C464" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="D464" t="s">
         <v>63</v>
@@ -19361,10 +19355,10 @@
         <v>13</v>
       </c>
       <c r="B465" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="C465" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="D465" t="s">
         <v>160</v>
@@ -19379,13 +19373,13 @@
         <v>81</v>
       </c>
       <c r="H465" t="s">
+        <v>986</v>
+      </c>
+      <c r="I465" t="s">
         <v>161</v>
       </c>
-      <c r="I465" t="s">
-        <v>162</v>
-      </c>
       <c r="J465" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="M465">
         <v>1</v>
@@ -19396,10 +19390,10 @@
         <v>13</v>
       </c>
       <c r="B466" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="C466" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="D466" t="s">
         <v>80</v>
@@ -19431,13 +19425,13 @@
         <v>13</v>
       </c>
       <c r="B467" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="C467" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="D467" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E467">
         <v>4</v>
@@ -19449,10 +19443,10 @@
         <v>81</v>
       </c>
       <c r="H467" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I467" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J467" t="s">
         <v>97</v>
@@ -19466,13 +19460,13 @@
         <v>13</v>
       </c>
       <c r="B468" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="C468" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D468" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E468">
         <v>5</v>
@@ -19484,7 +19478,7 @@
         <v>81</v>
       </c>
       <c r="H468" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I468" t="s">
         <v>87</v>
@@ -19501,10 +19495,10 @@
         <v>13</v>
       </c>
       <c r="B469" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C469" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D469" t="s">
         <v>80</v>
@@ -19536,10 +19530,10 @@
         <v>13</v>
       </c>
       <c r="B470" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="C470" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="D470" t="s">
         <v>16</v>
@@ -19571,13 +19565,13 @@
         <v>13</v>
       </c>
       <c r="B471" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C471" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="D471" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E471">
         <v>4</v>
@@ -19589,13 +19583,13 @@
         <v>81</v>
       </c>
       <c r="H471" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="I471" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="J471" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="M471">
         <v>1</v>
@@ -19606,10 +19600,10 @@
         <v>13</v>
       </c>
       <c r="B472" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C472" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="D472" t="s">
         <v>35</v>
@@ -19627,7 +19621,7 @@
         <v>152</v>
       </c>
       <c r="I472" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J472" t="s">
         <v>84</v>
@@ -19641,13 +19635,13 @@
         <v>13</v>
       </c>
       <c r="B473" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C473" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="D473" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E473">
         <v>4</v>
@@ -19659,7 +19653,7 @@
         <v>81</v>
       </c>
       <c r="H473" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I473" t="s">
         <v>87</v>
@@ -19676,10 +19670,10 @@
         <v>13</v>
       </c>
       <c r="B474" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C474" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="D474" t="s">
         <v>108</v>
@@ -19711,13 +19705,13 @@
         <v>13</v>
       </c>
       <c r="B475" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="C475" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="D475" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="E475">
         <v>4</v>
@@ -19729,13 +19723,13 @@
         <v>81</v>
       </c>
       <c r="H475" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="I475" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="J475" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="M475">
         <v>1</v>
@@ -19746,10 +19740,10 @@
         <v>13</v>
       </c>
       <c r="B476" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="C476" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="D476" t="s">
         <v>80</v>
@@ -19781,10 +19775,10 @@
         <v>13</v>
       </c>
       <c r="B477" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="C477" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="D477" t="s">
         <v>60</v>
@@ -19816,10 +19810,10 @@
         <v>13</v>
       </c>
       <c r="B478" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="C478" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="D478" t="s">
         <v>63</v>
@@ -19851,10 +19845,10 @@
         <v>13</v>
       </c>
       <c r="B479" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="C479" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="D479" t="s">
         <v>151</v>
@@ -19886,10 +19880,10 @@
         <v>13</v>
       </c>
       <c r="B480" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="C480" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="D480" t="s">
         <v>156</v>
@@ -19907,7 +19901,7 @@
         <v>140</v>
       </c>
       <c r="I480" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="J480" t="s">
         <v>142</v>
@@ -19921,13 +19915,13 @@
         <v>13</v>
       </c>
       <c r="B481" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C481" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D481" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E481">
         <v>9</v>
@@ -19939,10 +19933,10 @@
         <v>81</v>
       </c>
       <c r="H481" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I481" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="J481" t="s">
         <v>88</v>
@@ -19956,13 +19950,13 @@
         <v>13</v>
       </c>
       <c r="B482" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="C482" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="D482" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E482">
         <v>4</v>
@@ -19974,7 +19968,7 @@
         <v>81</v>
       </c>
       <c r="H482" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I482" t="s">
         <v>87</v>
@@ -19991,13 +19985,13 @@
         <v>13</v>
       </c>
       <c r="B483" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="C483" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="D483" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E483">
         <v>2</v>
@@ -20009,10 +20003,10 @@
         <v>81</v>
       </c>
       <c r="H483" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I483" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="J483" t="s">
         <v>88</v>
@@ -20026,13 +20020,13 @@
         <v>13</v>
       </c>
       <c r="B484" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C484" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="D484" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E484">
         <v>10</v>
@@ -20047,7 +20041,7 @@
         <v>109</v>
       </c>
       <c r="I484" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J484" t="s">
         <v>111</v>
@@ -20061,10 +20055,10 @@
         <v>13</v>
       </c>
       <c r="B485" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="C485" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="D485" t="s">
         <v>60</v>
@@ -20096,10 +20090,10 @@
         <v>13</v>
       </c>
       <c r="B486" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="C486" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="D486" t="s">
         <v>80</v>
@@ -20131,10 +20125,10 @@
         <v>13</v>
       </c>
       <c r="B487" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="C487" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="D487" t="s">
         <v>80</v>
@@ -20166,10 +20160,10 @@
         <v>13</v>
       </c>
       <c r="B488" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="C488" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="D488" t="s">
         <v>60</v>
@@ -20201,13 +20195,13 @@
         <v>13</v>
       </c>
       <c r="B489" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="C489" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="D489" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E489">
         <v>8</v>
@@ -20219,10 +20213,10 @@
         <v>81</v>
       </c>
       <c r="H489" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I489" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="J489" t="s">
         <v>84</v>
@@ -20236,13 +20230,13 @@
         <v>13</v>
       </c>
       <c r="B490" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="C490" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="D490" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E490">
         <v>14</v>
@@ -20257,7 +20251,7 @@
         <v>82</v>
       </c>
       <c r="I490" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J490" t="s">
         <v>84</v>
@@ -20271,13 +20265,13 @@
         <v>13</v>
       </c>
       <c r="B491" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="C491" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="D491" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E491">
         <v>4</v>
@@ -20289,10 +20283,10 @@
         <v>81</v>
       </c>
       <c r="H491" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I491" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J491" t="s">
         <v>97</v>
@@ -20306,13 +20300,13 @@
         <v>13</v>
       </c>
       <c r="B492" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="C492" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="D492" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E492">
         <v>4</v>
@@ -20324,7 +20318,7 @@
         <v>81</v>
       </c>
       <c r="H492" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I492" t="s">
         <v>87</v>
@@ -20341,10 +20335,10 @@
         <v>13</v>
       </c>
       <c r="B493" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="C493" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="D493" t="s">
         <v>80</v>
@@ -20376,13 +20370,13 @@
         <v>13</v>
       </c>
       <c r="B494" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="C494" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="D494" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E494">
         <v>15</v>
@@ -20397,7 +20391,7 @@
         <v>152</v>
       </c>
       <c r="I494" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J494" t="s">
         <v>84</v>
@@ -20411,10 +20405,10 @@
         <v>13</v>
       </c>
       <c r="B495" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="C495" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="D495" t="s">
         <v>71</v>
@@ -20446,13 +20440,13 @@
         <v>13</v>
       </c>
       <c r="B496" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="C496" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D496" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E496">
         <v>2</v>
@@ -20464,10 +20458,10 @@
         <v>81</v>
       </c>
       <c r="H496" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I496" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="J496" t="s">
         <v>88</v>
@@ -20481,13 +20475,13 @@
         <v>13</v>
       </c>
       <c r="B497" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="C497" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="D497" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E497">
         <v>5</v>
@@ -20499,7 +20493,7 @@
         <v>81</v>
       </c>
       <c r="H497" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I497" t="s">
         <v>87</v>
@@ -20516,10 +20510,10 @@
         <v>13</v>
       </c>
       <c r="B498" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="C498" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="D498" t="s">
         <v>108</v>
@@ -20551,13 +20545,13 @@
         <v>13</v>
       </c>
       <c r="B499" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="C499" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="D499" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E499">
         <v>6</v>
@@ -20586,10 +20580,10 @@
         <v>13</v>
       </c>
       <c r="B500" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="C500" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="D500" t="s">
         <v>63</v>
@@ -20621,10 +20615,10 @@
         <v>13</v>
       </c>
       <c r="B501" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="C501" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="D501" t="s">
         <v>35</v>
@@ -20642,7 +20636,7 @@
         <v>152</v>
       </c>
       <c r="I501" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J501" t="s">
         <v>84</v>
@@ -20656,13 +20650,13 @@
         <v>13</v>
       </c>
       <c r="B502" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="C502" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="D502" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E502">
         <v>4</v>
@@ -20674,10 +20668,10 @@
         <v>81</v>
       </c>
       <c r="H502" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I502" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J502" t="s">
         <v>97</v>
@@ -20691,13 +20685,13 @@
         <v>13</v>
       </c>
       <c r="B503" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="C503" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="D503" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E503">
         <v>4</v>
@@ -20709,7 +20703,7 @@
         <v>81</v>
       </c>
       <c r="H503" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I503" t="s">
         <v>87</v>
@@ -20726,10 +20720,10 @@
         <v>13</v>
       </c>
       <c r="B504" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="C504" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="D504" t="s">
         <v>80</v>
@@ -20761,10 +20755,10 @@
         <v>13</v>
       </c>
       <c r="B505" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="C505" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="D505" t="s">
         <v>114</v>
@@ -20779,7 +20773,7 @@
         <v>81</v>
       </c>
       <c r="H505" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I505" t="s">
         <v>87</v>
@@ -20792,6 +20786,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M505" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>